--- a/output/learner_integrated_phase4A_4D/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
+++ b/output/learner_integrated_phase4A_4D/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
@@ -1,1235 +1,1242 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangpinyi\Desktop\Lastinger\assessment-feedback-analysis\output\learner_integrated_phase4A_4D\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B7D30B579F4B4CA8F1E4AA7282CE9C4D7D0EDAA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Headline Metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phase 4A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phase 4B" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Phase 4C" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Phase 4D" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Figures" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Headline Metrics" sheetId="2" r:id="rId2"/>
+    <sheet name="Phase 4A" sheetId="3" r:id="rId3"/>
+    <sheet name="Phase 4B" sheetId="4" r:id="rId4"/>
+    <sheet name="Phase 4C" sheetId="5" r:id="rId5"/>
+    <sheet name="Phase 4D" sheetId="6" r:id="rId6"/>
+    <sheet name="Figures" sheetId="7" r:id="rId7"/>
+    <sheet name="Sources" sheetId="8" r:id="rId8"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
-  <si>
-    <t xml:space="preserve">Learner Survey: Integrated Phase 4A-4D Results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The sequence from feedback experience to AI comfort, perceived usefulness, and preferred feedback model is an interpretive and associational synthesis, not a causal or mediation model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Executive Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">analytic_focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reporting_caution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback-experience measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The four feedback items formed a strongly reliable ordinal index (ordinal alpha = 0.903). The composite mean was 4.80, and 71.2% received the maximum score.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The current feedback process provides a strong experiential foundation, but the severe ceiling effect limits differentiation among highly positive experiences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The four-item CFA was inadmissible; the scale should be described as a reliable unit-weighted index rather than a confirmed latent factor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI comfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greater AI comfort was associated with extensive prior AI experience, greater awareness of AI use, and more favorable feedback experience. Adjusted comfort probability increased from 48.6% among respondents not aware of AI use to 82.2% among fully aware respondents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI readiness corresponds with prior exposure, transparency, and learners' experiences of the feedback process.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI awareness affected both the location and scale components of comfort, so adjusted probabilities are more interpretable than one proportional-odds ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived AI usefulness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8% agreed that AI-generated feedback could be as useful as human feedback. Adjusted agreement increased from 1.1% to 90.4% across the AI-comfort scale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI comfort is the clearest bridge between general readiness and believing that AI-generated feedback is useful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The selected location-scale model had an elevated Hessian condition number, so emphasis should remain on adjusted probabilities and the overall pattern.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred feedback model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7% preferred a model involving universal human review. The adjusted probability of an AI-forward model increased from 6.0% to 65.0% across perceived AI-usefulness levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learners distinguish between viewing AI as useful and granting AI unrestricted responsibility for feedback or grading.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The multinomial analysis was associational, and sparse predictor-by-outcome cells warrant caution with individual category-specific estimates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-Phase Synthesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence_stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contributing_phases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">main_evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integrated_interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inference_boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Feedback foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinal alpha = 0.903; composite mean = 4.80; maximum-score percentage = 71.2%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondents evaluated the existing feedback process exceptionally positively, creating a favorable but compressed foundation for considering AI-supported feedback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The scale findings describe measurement quality and response distribution; they do not establish causal effects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Readiness for AI-supported feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phases 4A and 4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extensive prior AI experience, AI awareness, and feedback experience were associated with AI comfort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comfort with AI appears connected to familiarity, transparency, and experience rather than functioning only as a fixed personal attitude.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Phase 4B associations do not demonstrate that awareness or feedback experience causes comfort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Perceived usefulness of AI feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phases 4B and 4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted agreement that AI feedback could be as useful as human feedback increased from 1.1% to 90.4% across AI-comfort levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comfort is more proximally connected to perceived AI usefulness than the general feedback-experience index.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The sequence from comfort to usefulness is an analytic synthesis, not a tested mediation model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Preferred implementation model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phases 4C and 4D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7% preferred universal human review, while adjusted AI-forward preference increased from 6.0% to 65.0% across perceived usefulness levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greater perceived usefulness corresponds with more AI-forward preferences, but learners continue to place substantial value on universal human review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The preference results show associations and adjusted probabilities, not causal effects of usefulness on model choice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrated Headline Metrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistical_evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytic sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 170 respondents had complete data for the four feedback items.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinal alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The four-item index demonstrated strong ordinal reliability.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average polychoric correlation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The feedback items were strongly related at the latent-response level.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range of polychoric correlations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524 to 0.901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All item pairs were positively associated, although the strength varied across pairs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance represented by first component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A dominant first component supported summarizing the items with one overall feedback-experience score.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback-experience composite mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learners reported exceptionally favorable feedback experiences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback-experience composite SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The composite displayed limited variability.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpret regression estimates in light of the restricted score variation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum-score respondents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The pronounced ceiling effect limits differentiation among respondents with very positive feedback experiences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do not treat the composite as finely distinguishing highly satisfied respondents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary-sensitivity composite correlation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The four-item and three-item scores produced nearly identical respondent rankings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measurement decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retain the four-item unit-weighted index; do not interpret the inadmissible CFA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The four-item index is retained for substantive coverage, with the three-item version used as a sensitivity measure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do not report CFA-based omega or global CFA fit because the four-item CFA was inadmissible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extensive prior AI experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location coefficient = 4.81, p = 0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondents with extensive prior AI experience reported greater comfort with AI-supported feedback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location coefficient = 1.35, p &lt; .001; log-scale coefficient = 0.258, p = 0.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greater awareness corresponded with higher comfort, but awareness also changed the dispersion of the latent comfort response.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awareness affected both location and scale; use adjusted probabilities for interpretation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location coefficient per 0.5-point increase = 0.669, p = 0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More favorable feedback experiences were associated with greater AI comfort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted comfort probability by awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability of somewhat or strongly agreeing with AI comfort: 48.6% among respondents not aware of AI use, 71.8% among somewhat aware respondents, and 82.2% among fully aware respondents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The adjusted probabilities show a substantial increase in comfort across awareness levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative-link location-scale model; AIC = 406.33.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Because awareness affected both location and scale, adjusted probabilities are preferable to a single proportional-odds ratio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hessian condition number was elevated, so large individual coefficients should be interpreted cautiously.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed perceived usefulness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117 of 170 respondents (68.8%) somewhat or strongly agreed that AI-generated feedback could be as useful as human feedback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A majority of respondents viewed AI-generated feedback as potentially comparable in usefulness to human feedback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location coefficient = 3.68, p &lt; .001; log-scale coefficient = 0.272, p = 0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI comfort was strongly associated with perceived AI usefulness and also affected latent-response dispersion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comfort affected both location and scale; adjusted probabilities are the primary effect-size presentation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted usefulness probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted agreement probability increased from 1.1% at the lowest comfort level to 90.4% at the highest comfort level.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comfort clearly distinguished respondents with low versus high adjusted probabilities of viewing AI feedback as useful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location-scale model improvement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likelihood-ratio test p = 0.004; selected-model AIC = 359.23.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The location-scale model fit better than the proportional-odds benchmark.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The selected model had an elevated Hessian condition number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback-experience contribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding feedback experience after AI comfort: likelihood-ratio test p = 0.917.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback experience did not improve the usefulness model after AI comfort was included.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Largest preferred-model category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-led grading with AI support: 66 of 169 respondents (39.1%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The most common single preference retained instructor control and used AI only as a support tool.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111 of 169 respondents (65.7%) preferred universal human review. Among respondents with a directional preference, the percentage was 79.9%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learners generally accepted AI assistance while retaining a strong preference for universal human accountability.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding perceived usefulness to a feedback-only model: likelihood-ratio test p &lt; .001.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived AI usefulness substantially distinguished preferred feedback models.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpret omnibus likelihood-ratio tests alongside category-specific coefficients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding feedback experience to a usefulness-only model: likelihood-ratio test p = 0.010.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback experience improved overall model fit even though its individual category-specific Wald coefficients were not statistically significant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted AI-forward preference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted probability of an AI-forward feedback model increased from 6.0% among respondents who strongly disagreed that AI feedback was as useful as human feedback to 65.0% among those who strongly agreed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More favorable perceptions of AI usefulness corresponded with substantially more AI-forward implementation preferences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The results are associational, and some predictor-by-outcome cells were sparse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4A: Feedback-Experience Scale Diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headline Results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polychoric Correlation Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubric_clear_aligned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_specific_relevant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_helped_improve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_timely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinal Item Diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ordinal_item_rest_correlation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ordinal_alpha_if_deleted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valid_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_deviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minimum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maximum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maximum_score_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maximum_score_percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four-item feedback-experience composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three-item composite excluding specificity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measurement Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary variable type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit-weighted four-item mean/index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary number of items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary raw alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary standardized alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary ordinal alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four-item CFA admissible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary composite mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary composite SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary maximum-score percentage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_experience_3item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity number of items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity raw alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity observed omega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correlation between primary and sensitivity scores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4B: AI Comfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headline Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Model Fit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected_model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">analytic_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_of_parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maximum_absolute_gradient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hessian_condition_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final linear awareness-scale model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified Model Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">effect_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value_display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confidence_low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confidence_high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extensive prior AI experience versus no experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">= 0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI awareness: location effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; .001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback experience: 0.5-point increase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">= 0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI awareness: log-scale effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">= 0.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted Probabilities by AI Awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_awareness_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">predicted_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not aware at all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somewhat aware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fully aware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted Probabilities by Feedback Experience and AI Awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_experience_half_point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Analysis Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_comfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative-link location-scale model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location predictors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prior AI experience; AI awareness score; feedback-experience composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale predictor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI awareness score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flexible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final model AIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final model BIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">437.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final model log likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-193.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awareness-scale versus benchmark LRT p-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factor-coded versus linear scale LRT p-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary effect-size presentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted predicted probabilities with 95% confidence intervals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benchmark model role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity/benchmark proportional-odds odds ratios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Displayed feedback-composite range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00 to 5.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason for restricted plotted range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1% of respondents scored within the displayed range; 71.2% scored at the maximum of 5.00.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4C: Perceived AI Usefulness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome Distribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_usefulness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strongly disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somewhat disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neither agree nor disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somewhat agree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strongly agree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">convergence_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">convergence_message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comfort-added AI-comfort scale model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute and relative convergence criteria were met</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified AI-Comfort Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI comfort: location effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI comfort: log-scale effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">= 0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted Agreement Probabilities by AI Comfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_comfort_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confidence_low_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">confidence_high_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label_y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent_label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proportional-Odds Versus Location-Scale Comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no.par</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR.stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;Chisq)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback-Experience Addition Comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4D: Preferred Feedback Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred-Model Distribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preferred_model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-led grading; AI support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI initial feedback; universal human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-led feedback; disputed-only human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No preference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-Review Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">denominator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid preferred-model responses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expressed a directional model preference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred universal human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred disputed-only human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred human-led grading with AI support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred AI initial feedback with universal human review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal review among directional preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-led grading among universal-review preferences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Model Selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_addition_likelihood_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_addition_df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feedback_addition_p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usefulness-and-feedback multinomial model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preferred_model ~ ai_usefulness_score + feedback_experience_half_point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report-Ready Multinomial Coefficients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference_category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relative_risk_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ai_usefulness_score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduced-Model Likelihood-Ratio Comparisons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smaller_model_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">larger_model_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smaller_model_log_likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">larger_model_log_likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">likelihood_ratio_chisquare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usefulness only versus usefulness plus feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback only versus feedback plus usefulness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouped Adjusted Probabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">observed_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preference_group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">predicted_percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-led grading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-forward feedback model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum-Likelihood Versus Bias-Reduced Estimates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate_maximum_likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate_mean_bias_reduced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relative_risk_ratio_maximum_likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relative_risk_ratio_mean_bias_reduced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">absolute_estimate_difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent_RRR_difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report-Ready Figures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4A: Feedback-Experience Reliability Diagnostics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4B: Adjusted AI-Comfort Probability by AI Awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4C: Adjusted Perceived-Usefulness Probability by AI Comfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4D: Adjusted Probabilities of Preferred Feedback Models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analysis Source Manifest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">size_kb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4A analysis objects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDS analysis source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/phase4A_analysis_objects.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4A analysis data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_analysis_phase4A_with_composites.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4B final analysis objects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_final_analysis_objects.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4C final checkpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_final_analysis_checkpoint.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4C complete-case data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/learner_analysis_phase4C_complete_cases.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4D final checkpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_final_analysis_checkpoint.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4D complete-case data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/learner_analysis_phase4D_complete_cases.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNG figure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_feedback_reliability_plot.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_adjusted_probability_by_awareness.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_adjusted_usefulness_probability.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_adjusted_preferred_model_probabilities.png</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
+  <si>
+    <t>Learner Survey: Integrated Phase 4A-4D Results</t>
+  </si>
+  <si>
+    <t>The sequence from feedback experience to AI comfort, perceived usefulness, and preferred feedback model is an interpretive and associational synthesis, not a causal or mediation model.</t>
+  </si>
+  <si>
+    <t>Executive Summary</t>
+  </si>
+  <si>
+    <t>phase</t>
+  </si>
+  <si>
+    <t>analytic_focus</t>
+  </si>
+  <si>
+    <t>key_result</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>reporting_caution</t>
+  </si>
+  <si>
+    <t>Phase 4A</t>
+  </si>
+  <si>
+    <t>Feedback-experience measurement</t>
+  </si>
+  <si>
+    <t>The four feedback items formed a strongly reliable ordinal index (ordinal alpha = 0.903). The composite mean was 4.80, and 71.2% received the maximum score.</t>
+  </si>
+  <si>
+    <t>The current feedback process provides a strong experiential foundation, but the severe ceiling effect limits differentiation among highly positive experiences.</t>
+  </si>
+  <si>
+    <t>The four-item CFA was inadmissible; the scale should be described as a reliable unit-weighted index rather than a confirmed latent factor.</t>
+  </si>
+  <si>
+    <t>Phase 4B</t>
+  </si>
+  <si>
+    <t>AI comfort</t>
+  </si>
+  <si>
+    <t>Greater AI comfort was associated with extensive prior AI experience, greater awareness of AI use, and more favorable feedback experience. Adjusted comfort probability increased from 48.6% among respondents not aware of AI use to 82.2% among fully aware respondents.</t>
+  </si>
+  <si>
+    <t>AI readiness corresponds with prior exposure, transparency, and learners' experiences of the feedback process.</t>
+  </si>
+  <si>
+    <t>AI awareness affected both the location and scale components of comfort, so adjusted probabilities are more interpretable than one proportional-odds ratio.</t>
+  </si>
+  <si>
+    <t>Phase 4C</t>
+  </si>
+  <si>
+    <t>Perceived AI usefulness</t>
+  </si>
+  <si>
+    <t>68.8% agreed that AI-generated feedback could be as useful as human feedback. Adjusted agreement increased from 1.1% to 90.4% across the AI-comfort scale.</t>
+  </si>
+  <si>
+    <t>AI comfort is the clearest bridge between general readiness and believing that AI-generated feedback is useful.</t>
+  </si>
+  <si>
+    <t>The selected location-scale model had an elevated Hessian condition number, so emphasis should remain on adjusted probabilities and the overall pattern.</t>
+  </si>
+  <si>
+    <t>Phase 4D</t>
+  </si>
+  <si>
+    <t>Preferred feedback model</t>
+  </si>
+  <si>
+    <t>65.7% preferred a model involving universal human review. The adjusted probability of an AI-forward model increased from 6.0% to 65.0% across perceived AI-usefulness levels.</t>
+  </si>
+  <si>
+    <t>Learners distinguish between viewing AI as useful and granting AI unrestricted responsibility for feedback or grading.</t>
+  </si>
+  <si>
+    <t>The multinomial analysis was associational, and sparse predictor-by-outcome cells warrant caution with individual category-specific estimates.</t>
+  </si>
+  <si>
+    <t>Cross-Phase Synthesis</t>
+  </si>
+  <si>
+    <t>evidence_stage</t>
+  </si>
+  <si>
+    <t>contributing_phases</t>
+  </si>
+  <si>
+    <t>main_evidence</t>
+  </si>
+  <si>
+    <t>integrated_interpretation</t>
+  </si>
+  <si>
+    <t>inference_boundary</t>
+  </si>
+  <si>
+    <t>1. Feedback foundation</t>
+  </si>
+  <si>
+    <t>Ordinal alpha = 0.903; composite mean = 4.80; maximum-score percentage = 71.2%.</t>
+  </si>
+  <si>
+    <t>Respondents evaluated the existing feedback process exceptionally positively, creating a favorable but compressed foundation for considering AI-supported feedback.</t>
+  </si>
+  <si>
+    <t>The scale findings describe measurement quality and response distribution; they do not establish causal effects.</t>
+  </si>
+  <si>
+    <t>2. Readiness for AI-supported feedback</t>
+  </si>
+  <si>
+    <t>Phases 4A and 4B</t>
+  </si>
+  <si>
+    <t>Extensive prior AI experience, AI awareness, and feedback experience were associated with AI comfort.</t>
+  </si>
+  <si>
+    <t>Comfort with AI appears connected to familiarity, transparency, and experience rather than functioning only as a fixed personal attitude.</t>
+  </si>
+  <si>
+    <t>The Phase 4B associations do not demonstrate that awareness or feedback experience causes comfort.</t>
+  </si>
+  <si>
+    <t>3. Perceived usefulness of AI feedback</t>
+  </si>
+  <si>
+    <t>Phases 4B and 4C</t>
+  </si>
+  <si>
+    <t>Adjusted agreement that AI feedback could be as useful as human feedback increased from 1.1% to 90.4% across AI-comfort levels.</t>
+  </si>
+  <si>
+    <t>Comfort is more proximally connected to perceived AI usefulness than the general feedback-experience index.</t>
+  </si>
+  <si>
+    <t>The sequence from comfort to usefulness is an analytic synthesis, not a tested mediation model.</t>
+  </si>
+  <si>
+    <t>4. Preferred implementation model</t>
+  </si>
+  <si>
+    <t>Phases 4C and 4D</t>
+  </si>
+  <si>
+    <t>65.7% preferred universal human review, while adjusted AI-forward preference increased from 6.0% to 65.0% across perceived usefulness levels.</t>
+  </si>
+  <si>
+    <t>Greater perceived usefulness corresponds with more AI-forward preferences, but learners continue to place substantial value on universal human review.</t>
+  </si>
+  <si>
+    <t>The preference results show associations and adjusted probabilities, not causal effects of usefulness on model choice.</t>
+  </si>
+  <si>
+    <t>Integrated Headline Metrics</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>statistical_evidence</t>
+  </si>
+  <si>
+    <t>Analytic sample</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>All 170 respondents had complete data for the four feedback items.</t>
+  </si>
+  <si>
+    <t>Ordinal alpha</t>
+  </si>
+  <si>
+    <t>0.903</t>
+  </si>
+  <si>
+    <t>The four-item index demonstrated strong ordinal reliability.</t>
+  </si>
+  <si>
+    <t>Average polychoric correlation</t>
+  </si>
+  <si>
+    <t>0.701</t>
+  </si>
+  <si>
+    <t>The feedback items were strongly related at the latent-response level.</t>
+  </si>
+  <si>
+    <t>Range of polychoric correlations</t>
+  </si>
+  <si>
+    <t>0.524 to 0.901</t>
+  </si>
+  <si>
+    <t>All item pairs were positively associated, although the strength varied across pairs.</t>
+  </si>
+  <si>
+    <t>Variance represented by first component</t>
+  </si>
+  <si>
+    <t>78.0%</t>
+  </si>
+  <si>
+    <t>A dominant first component supported summarizing the items with one overall feedback-experience score.</t>
+  </si>
+  <si>
+    <t>Feedback-experience composite mean</t>
+  </si>
+  <si>
+    <t>4.80</t>
+  </si>
+  <si>
+    <t>Learners reported exceptionally favorable feedback experiences.</t>
+  </si>
+  <si>
+    <t>Feedback-experience composite SD</t>
+  </si>
+  <si>
+    <t>0.437</t>
+  </si>
+  <si>
+    <t>The composite displayed limited variability.</t>
+  </si>
+  <si>
+    <t>Interpret regression estimates in light of the restricted score variation.</t>
+  </si>
+  <si>
+    <t>Maximum-score respondents</t>
+  </si>
+  <si>
+    <t>71.2%</t>
+  </si>
+  <si>
+    <t>The pronounced ceiling effect limits differentiation among respondents with very positive feedback experiences.</t>
+  </si>
+  <si>
+    <t>Do not treat the composite as finely distinguishing highly satisfied respondents.</t>
+  </si>
+  <si>
+    <t>Primary-sensitivity composite correlation</t>
+  </si>
+  <si>
+    <t>0.981</t>
+  </si>
+  <si>
+    <t>The four-item and three-item scores produced nearly identical respondent rankings.</t>
+  </si>
+  <si>
+    <t>Measurement decision</t>
+  </si>
+  <si>
+    <t>Retain the four-item unit-weighted index; do not interpret the inadmissible CFA.</t>
+  </si>
+  <si>
+    <t>The four-item index is retained for substantive coverage, with the three-item version used as a sensitivity measure.</t>
+  </si>
+  <si>
+    <t>Do not report CFA-based omega or global CFA fit because the four-item CFA was inadmissible.</t>
+  </si>
+  <si>
+    <t>Extensive prior AI experience</t>
+  </si>
+  <si>
+    <t>Location coefficient = 4.81, p = 0.015</t>
+  </si>
+  <si>
+    <t>Respondents with extensive prior AI experience reported greater comfort with AI-supported feedback.</t>
+  </si>
+  <si>
+    <t>AI awareness</t>
+  </si>
+  <si>
+    <t>Location coefficient = 1.35, p &lt; .001; log-scale coefficient = 0.258, p = 0.031</t>
+  </si>
+  <si>
+    <t>Greater awareness corresponded with higher comfort, but awareness also changed the dispersion of the latent comfort response.</t>
+  </si>
+  <si>
+    <t>Awareness affected both location and scale; use adjusted probabilities for interpretation.</t>
+  </si>
+  <si>
+    <t>Feedback experience</t>
+  </si>
+  <si>
+    <t>Location coefficient per 0.5-point increase = 0.669, p = 0.008</t>
+  </si>
+  <si>
+    <t>More favorable feedback experiences were associated with greater AI comfort.</t>
+  </si>
+  <si>
+    <t>Adjusted comfort probability by awareness</t>
+  </si>
+  <si>
+    <t>Probability of somewhat or strongly agreeing with AI comfort: 48.6% among respondents not aware of AI use, 71.8% among somewhat aware respondents, and 82.2% among fully aware respondents.</t>
+  </si>
+  <si>
+    <t>The adjusted probabilities show a substantial increase in comfort across awareness levels.</t>
+  </si>
+  <si>
+    <t>Model form</t>
+  </si>
+  <si>
+    <t>Cumulative-link location-scale model; AIC = 406.33.</t>
+  </si>
+  <si>
+    <t>Because awareness affected both location and scale, adjusted probabilities are preferable to a single proportional-odds ratio.</t>
+  </si>
+  <si>
+    <t>The Hessian condition number was elevated, so large individual coefficients should be interpreted cautiously.</t>
+  </si>
+  <si>
+    <t>Observed perceived usefulness</t>
+  </si>
+  <si>
+    <t>117 of 170 respondents (68.8%) somewhat or strongly agreed that AI-generated feedback could be as useful as human feedback.</t>
+  </si>
+  <si>
+    <t>A majority of respondents viewed AI-generated feedback as potentially comparable in usefulness to human feedback.</t>
+  </si>
+  <si>
+    <t>Location coefficient = 3.68, p &lt; .001; log-scale coefficient = 0.272, p = 0.005</t>
+  </si>
+  <si>
+    <t>AI comfort was strongly associated with perceived AI usefulness and also affected latent-response dispersion.</t>
+  </si>
+  <si>
+    <t>Comfort affected both location and scale; adjusted probabilities are the primary effect-size presentation.</t>
+  </si>
+  <si>
+    <t>Adjusted usefulness probability</t>
+  </si>
+  <si>
+    <t>Adjusted agreement probability increased from 1.1% at the lowest comfort level to 90.4% at the highest comfort level.</t>
+  </si>
+  <si>
+    <t>Comfort clearly distinguished respondents with low versus high adjusted probabilities of viewing AI feedback as useful.</t>
+  </si>
+  <si>
+    <t>Location-scale model improvement</t>
+  </si>
+  <si>
+    <t>Likelihood-ratio test p = 0.004; selected-model AIC = 359.23.</t>
+  </si>
+  <si>
+    <t>The location-scale model fit better than the proportional-odds benchmark.</t>
+  </si>
+  <si>
+    <t>The selected model had an elevated Hessian condition number.</t>
+  </si>
+  <si>
+    <t>Feedback-experience contribution</t>
+  </si>
+  <si>
+    <t>Adding feedback experience after AI comfort: likelihood-ratio test p = 0.917.</t>
+  </si>
+  <si>
+    <t>Feedback experience did not improve the usefulness model after AI comfort was included.</t>
+  </si>
+  <si>
+    <t>Largest preferred-model category</t>
+  </si>
+  <si>
+    <t>Human-led grading with AI support: 66 of 169 respondents (39.1%).</t>
+  </si>
+  <si>
+    <t>The most common single preference retained instructor control and used AI only as a support tool.</t>
+  </si>
+  <si>
+    <t>Universal human review</t>
+  </si>
+  <si>
+    <t>111 of 169 respondents (65.7%) preferred universal human review. Among respondents with a directional preference, the percentage was 79.9%.</t>
+  </si>
+  <si>
+    <t>Learners generally accepted AI assistance while retaining a strong preference for universal human accountability.</t>
+  </si>
+  <si>
+    <t>Adding perceived usefulness to a feedback-only model: likelihood-ratio test p &lt; .001.</t>
+  </si>
+  <si>
+    <t>Perceived AI usefulness substantially distinguished preferred feedback models.</t>
+  </si>
+  <si>
+    <t>Interpret omnibus likelihood-ratio tests alongside category-specific coefficients.</t>
+  </si>
+  <si>
+    <t>Adding feedback experience to a usefulness-only model: likelihood-ratio test p = 0.010.</t>
+  </si>
+  <si>
+    <t>Feedback experience improved overall model fit even though its individual category-specific Wald coefficients were not statistically significant.</t>
+  </si>
+  <si>
+    <t>Adjusted AI-forward preference</t>
+  </si>
+  <si>
+    <t>Adjusted probability of an AI-forward feedback model increased from 6.0% among respondents who strongly disagreed that AI feedback was as useful as human feedback to 65.0% among those who strongly agreed.</t>
+  </si>
+  <si>
+    <t>More favorable perceptions of AI usefulness corresponded with substantially more AI-forward implementation preferences.</t>
+  </si>
+  <si>
+    <t>The results are associational, and some predictor-by-outcome cells were sparse.</t>
+  </si>
+  <si>
+    <t>Phase 4A: Feedback-Experience Scale Diagnostics</t>
+  </si>
+  <si>
+    <t>Headline Results</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>Polychoric Correlation Matrix</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>rubric_clear_aligned</t>
+  </si>
+  <si>
+    <t>feedback_specific_relevant</t>
+  </si>
+  <si>
+    <t>feedback_helped_improve</t>
+  </si>
+  <si>
+    <t>feedback_timely</t>
+  </si>
+  <si>
+    <t>Ordinal Item Diagnostics</t>
+  </si>
+  <si>
+    <t>ordinal_item_rest_correlation</t>
+  </si>
+  <si>
+    <t>ordinal_alpha_if_deleted</t>
+  </si>
+  <si>
+    <t>Composite Summary</t>
+  </si>
+  <si>
+    <t>composite</t>
+  </si>
+  <si>
+    <t>valid_n</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>standard_deviation</t>
+  </si>
+  <si>
+    <t>minimum</t>
+  </si>
+  <si>
+    <t>maximum</t>
+  </si>
+  <si>
+    <t>maximum_score_n</t>
+  </si>
+  <si>
+    <t>maximum_score_percent</t>
+  </si>
+  <si>
+    <t>Four-item feedback-experience composite</t>
+  </si>
+  <si>
+    <t>Three-item composite excluding specificity</t>
+  </si>
+  <si>
+    <t>Measurement Decision</t>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>Primary variable</t>
+  </si>
+  <si>
+    <t>feedback_experience</t>
+  </si>
+  <si>
+    <t>Primary variable type</t>
+  </si>
+  <si>
+    <t>Unit-weighted four-item mean/index</t>
+  </si>
+  <si>
+    <t>Primary number of items</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Primary raw alpha</t>
+  </si>
+  <si>
+    <t>0.781</t>
+  </si>
+  <si>
+    <t>Primary standardized alpha</t>
+  </si>
+  <si>
+    <t>0.800</t>
+  </si>
+  <si>
+    <t>Primary ordinal alpha</t>
+  </si>
+  <si>
+    <t>Four-item CFA admissible</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Primary composite mean</t>
+  </si>
+  <si>
+    <t>4.800</t>
+  </si>
+  <si>
+    <t>Primary composite SD</t>
+  </si>
+  <si>
+    <t>Primary maximum-score percentage</t>
+  </si>
+  <si>
+    <t>Sensitivity variable</t>
+  </si>
+  <si>
+    <t>feedback_experience_3item</t>
+  </si>
+  <si>
+    <t>Sensitivity number of items</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sensitivity raw alpha</t>
+  </si>
+  <si>
+    <t>0.631</t>
+  </si>
+  <si>
+    <t>Sensitivity observed omega</t>
+  </si>
+  <si>
+    <t>0.655</t>
+  </si>
+  <si>
+    <t>Correlation between primary and sensitivity scores</t>
+  </si>
+  <si>
+    <t>Phase 4B: AI Comfort</t>
+  </si>
+  <si>
+    <t>Headline Summary</t>
+  </si>
+  <si>
+    <t>finding</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t>Final Model Fit</t>
+  </si>
+  <si>
+    <t>selected_model</t>
+  </si>
+  <si>
+    <t>analytic_n</t>
+  </si>
+  <si>
+    <t>number_of_parameters</t>
+  </si>
+  <si>
+    <t>log_likelihood</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>maximum_absolute_gradient</t>
+  </si>
+  <si>
+    <t>hessian_condition_number</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Final linear awareness-scale model</t>
+  </si>
+  <si>
+    <t>logit</t>
+  </si>
+  <si>
+    <t>Verified Model Effects</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>effect_type</t>
+  </si>
+  <si>
+    <t>standard_error</t>
+  </si>
+  <si>
+    <t>z_value</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>p_value_display</t>
+  </si>
+  <si>
+    <t>confidence_low</t>
+  </si>
+  <si>
+    <t>confidence_high</t>
+  </si>
+  <si>
+    <t>Extensive prior AI experience versus no experience</t>
+  </si>
+  <si>
+    <t>Location effect</t>
+  </si>
+  <si>
+    <t>= 0.015</t>
+  </si>
+  <si>
+    <t>AI awareness: location effect</t>
+  </si>
+  <si>
+    <t>&lt; .001</t>
+  </si>
+  <si>
+    <t>Feedback experience: 0.5-point increase</t>
+  </si>
+  <si>
+    <t>= 0.008</t>
+  </si>
+  <si>
+    <t>AI awareness: log-scale effect</t>
+  </si>
+  <si>
+    <t>Scale effect</t>
+  </si>
+  <si>
+    <t>= 0.031</t>
+  </si>
+  <si>
+    <t>Adjusted Probabilities by AI Awareness</t>
+  </si>
+  <si>
+    <t>ai_awareness_score</t>
+  </si>
+  <si>
+    <t>ai_awareness</t>
+  </si>
+  <si>
+    <t>predicted_probability</t>
+  </si>
+  <si>
+    <t>Not aware at all</t>
+  </si>
+  <si>
+    <t>Somewhat aware</t>
+  </si>
+  <si>
+    <t>Fully aware</t>
+  </si>
+  <si>
+    <t>Adjusted Probabilities by Feedback Experience and AI Awareness</t>
+  </si>
+  <si>
+    <t>feedback_experience_half_point</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>Final Analysis Decision</t>
+  </si>
+  <si>
+    <t>Final outcome</t>
+  </si>
+  <si>
+    <t>ai_comfort</t>
+  </si>
+  <si>
+    <t>Final model</t>
+  </si>
+  <si>
+    <t>Cumulative-link location-scale model</t>
+  </si>
+  <si>
+    <t>Location predictors</t>
+  </si>
+  <si>
+    <t>Prior AI experience; AI awareness score; feedback-experience composite</t>
+  </si>
+  <si>
+    <t>Scale predictor</t>
+  </si>
+  <si>
+    <t>AI awareness score</t>
+  </si>
+  <si>
+    <t>Link function</t>
+  </si>
+  <si>
+    <t>Logit</t>
+  </si>
+  <si>
+    <t>Threshold structure</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>Final model AIC</t>
+  </si>
+  <si>
+    <t>406.33</t>
+  </si>
+  <si>
+    <t>Final model BIC</t>
+  </si>
+  <si>
+    <t>437.69</t>
+  </si>
+  <si>
+    <t>Final model log likelihood</t>
+  </si>
+  <si>
+    <t>-193.16</t>
+  </si>
+  <si>
+    <t>Awareness-scale versus benchmark LRT p-value</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>Factor-coded versus linear scale LRT p-value</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>Primary effect-size presentation</t>
+  </si>
+  <si>
+    <t>Adjusted predicted probabilities with 95% confidence intervals</t>
+  </si>
+  <si>
+    <t>Benchmark model role</t>
+  </si>
+  <si>
+    <t>Sensitivity/benchmark proportional-odds odds ratios</t>
+  </si>
+  <si>
+    <t>Displayed feedback-composite range</t>
+  </si>
+  <si>
+    <t>4.00 to 5.00</t>
+  </si>
+  <si>
+    <t>Reason for restricted plotted range</t>
+  </si>
+  <si>
+    <t>97.1% of respondents scored within the displayed range; 71.2% scored at the maximum of 5.00.</t>
+  </si>
+  <si>
+    <t>Phase 4C: Perceived AI Usefulness</t>
+  </si>
+  <si>
+    <t>Outcome Distribution</t>
+  </si>
+  <si>
+    <t>ai_usefulness</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t>Strongly disagree</t>
+  </si>
+  <si>
+    <t>Somewhat disagree</t>
+  </si>
+  <si>
+    <t>Neither agree nor disagree</t>
+  </si>
+  <si>
+    <t>Somewhat agree</t>
+  </si>
+  <si>
+    <t>Strongly agree</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>convergence_code</t>
+  </si>
+  <si>
+    <t>convergence_message</t>
+  </si>
+  <si>
+    <t>Comfort-added AI-comfort scale model</t>
+  </si>
+  <si>
+    <t>Absolute and relative convergence criteria were met</t>
+  </si>
+  <si>
+    <t>Verified AI-Comfort Effects</t>
+  </si>
+  <si>
+    <t>AI comfort: location effect</t>
+  </si>
+  <si>
+    <t>AI comfort: log-scale effect</t>
+  </si>
+  <si>
+    <t>= 0.005</t>
+  </si>
+  <si>
+    <t>Adjusted Agreement Probabilities by AI Comfort</t>
+  </si>
+  <si>
+    <t>ai_comfort_score</t>
+  </si>
+  <si>
+    <t>confidence_low_raw</t>
+  </si>
+  <si>
+    <t>confidence_high_raw</t>
+  </si>
+  <si>
+    <t>label_y</t>
+  </si>
+  <si>
+    <t>percent_label</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>Proportional-Odds Versus Location-Scale Comparison</t>
+  </si>
+  <si>
+    <t>no.par</t>
+  </si>
+  <si>
+    <t>logLik</t>
+  </si>
+  <si>
+    <t>LR.stat</t>
+  </si>
+  <si>
+    <t>Pr(&gt;Chisq)</t>
+  </si>
+  <si>
+    <t>Feedback-Experience Addition Comparison</t>
+  </si>
+  <si>
+    <t>Phase 4D: Preferred Feedback Model</t>
+  </si>
+  <si>
+    <t>Preferred-Model Distribution</t>
+  </si>
+  <si>
+    <t>preferred_model</t>
+  </si>
+  <si>
+    <t>Human-led grading; AI support</t>
+  </si>
+  <si>
+    <t>AI initial feedback; universal human review</t>
+  </si>
+  <si>
+    <t>AI-led feedback; disputed-only human review</t>
+  </si>
+  <si>
+    <t>No preference</t>
+  </si>
+  <si>
+    <t>Human-Review Summary</t>
+  </si>
+  <si>
+    <t>denominator</t>
+  </si>
+  <si>
+    <t>Valid preferred-model responses</t>
+  </si>
+  <si>
+    <t>Expressed a directional model preference</t>
+  </si>
+  <si>
+    <t>Preferred universal human review</t>
+  </si>
+  <si>
+    <t>Preferred disputed-only human review</t>
+  </si>
+  <si>
+    <t>Preferred human-led grading with AI support</t>
+  </si>
+  <si>
+    <t>Preferred AI initial feedback with universal human review</t>
+  </si>
+  <si>
+    <t>Universal review among directional preferences</t>
+  </si>
+  <si>
+    <t>Human-led grading among universal-review preferences</t>
+  </si>
+  <si>
+    <t>Final Model Selection</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>feedback_addition_likelihood_ratio</t>
+  </si>
+  <si>
+    <t>feedback_addition_df</t>
+  </si>
+  <si>
+    <t>feedback_addition_p_value</t>
+  </si>
+  <si>
+    <t>Usefulness-and-feedback multinomial model</t>
+  </si>
+  <si>
+    <t>preferred_model ~ ai_usefulness_score + feedback_experience_half_point</t>
+  </si>
+  <si>
+    <t>Report-Ready Multinomial Coefficients</t>
+  </si>
+  <si>
+    <t>outcome_category</t>
+  </si>
+  <si>
+    <t>reference_category</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>relative_risk_ratio</t>
+  </si>
+  <si>
+    <t>ai_usefulness_score</t>
+  </si>
+  <si>
+    <t>Reduced-Model Likelihood-Ratio Comparisons</t>
+  </si>
+  <si>
+    <t>comparison</t>
+  </si>
+  <si>
+    <t>smaller_model_n</t>
+  </si>
+  <si>
+    <t>larger_model_n</t>
+  </si>
+  <si>
+    <t>smaller_model_log_likelihood</t>
+  </si>
+  <si>
+    <t>larger_model_log_likelihood</t>
+  </si>
+  <si>
+    <t>likelihood_ratio_chisquare</t>
+  </si>
+  <si>
+    <t>Usefulness only versus usefulness plus feedback</t>
+  </si>
+  <si>
+    <t>Feedback only versus feedback plus usefulness</t>
+  </si>
+  <si>
+    <t>Grouped Adjusted Probabilities</t>
+  </si>
+  <si>
+    <t>observed_n</t>
+  </si>
+  <si>
+    <t>preference_group</t>
+  </si>
+  <si>
+    <t>predicted_percent</t>
+  </si>
+  <si>
+    <t>Human-led grading</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>AI-forward feedback model</t>
+  </si>
+  <si>
+    <t>6.0%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>67.2%</t>
+  </si>
+  <si>
+    <t>11.8%</t>
+  </si>
+  <si>
+    <t>21.0%</t>
+  </si>
+  <si>
+    <t>55.9%</t>
+  </si>
+  <si>
+    <t>22.6%</t>
+  </si>
+  <si>
+    <t>21.4%</t>
+  </si>
+  <si>
+    <t>40.3%</t>
+  </si>
+  <si>
+    <t>40.8%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
+  </si>
+  <si>
+    <t>22.2%</t>
+  </si>
+  <si>
+    <t>65.0%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>Maximum-Likelihood Versus Bias-Reduced Estimates</t>
+  </si>
+  <si>
+    <t>estimate_maximum_likelihood</t>
+  </si>
+  <si>
+    <t>estimate_mean_bias_reduced</t>
+  </si>
+  <si>
+    <t>relative_risk_ratio_maximum_likelihood</t>
+  </si>
+  <si>
+    <t>relative_risk_ratio_mean_bias_reduced</t>
+  </si>
+  <si>
+    <t>absolute_estimate_difference</t>
+  </si>
+  <si>
+    <t>percent_RRR_difference</t>
+  </si>
+  <si>
+    <t>Report-Ready Figures</t>
+  </si>
+  <si>
+    <t>Phase 4A: Feedback-Experience Reliability Diagnostics</t>
+  </si>
+  <si>
+    <t>Phase 4B: Adjusted AI-Comfort Probability by AI Awareness</t>
+  </si>
+  <si>
+    <t>Phase 4C: Adjusted Perceived-Usefulness Probability by AI Comfort</t>
+  </si>
+  <si>
+    <t>Phase 4D: Adjusted Probabilities of Preferred Feedback Models</t>
+  </si>
+  <si>
+    <t>Analysis Source Manifest</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>exists</t>
+  </si>
+  <si>
+    <t>size_kb</t>
+  </si>
+  <si>
+    <t>Phase 4A analysis objects</t>
+  </si>
+  <si>
+    <t>RDS analysis source</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/phase4A_analysis_objects.rds</t>
+  </si>
+  <si>
+    <t>Phase 4A analysis data</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_analysis_phase4A_with_composites.rds</t>
+  </si>
+  <si>
+    <t>Phase 4B final analysis objects</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_final_analysis_objects.rds</t>
+  </si>
+  <si>
+    <t>Phase 4C final checkpoint</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_final_analysis_checkpoint.rds</t>
+  </si>
+  <si>
+    <t>Phase 4C complete-case data</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/learner_analysis_phase4C_complete_cases.rds</t>
+  </si>
+  <si>
+    <t>Phase 4D final checkpoint</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_final_analysis_checkpoint.rds</t>
+  </si>
+  <si>
+    <t>Phase 4D complete-case data</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/learner_analysis_phase4D_complete_cases.rds</t>
+  </si>
+  <si>
+    <t>PNG figure</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_feedback_reliability_plot.png</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_adjusted_probability_by_awareness.png</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_adjusted_usefulness_probability.png</t>
+  </si>
+  <si>
+    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_adjusted_preferred_model_probabilities.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1238,22 +1245,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
       <sz val="11"/>
@@ -1278,9 +1285,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1308,126 +1319,155 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
-      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">3</xdr:row>
-      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
-    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Picture 1"/>
-        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+    <xdr:ext cx="9601200" cy="5852160"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-        </a:blip>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
-      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">31</xdr:row>
-      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
-    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Picture 2"/>
-        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+    <xdr:ext cx="9601200" cy="5852160"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-        </a:blip>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
-      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">59</xdr:row>
-      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
-    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="3" name="Picture 3"/>
-        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+    <xdr:ext cx="9601200" cy="5852160"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-        </a:blip>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
-      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">87</xdr:row>
-      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
-    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="4" name="Picture 4"/>
-        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+    <xdr:ext cx="9601200" cy="5852160"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-        </a:blip>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
@@ -1714,33 +1754,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="52.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="35" customHeight="1">
+    <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1757,7 +1796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="75" customHeight="1">
+    <row r="6" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1774,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -1791,7 +1830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="75" customHeight="1">
+    <row r="8" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1808,7 +1847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -1825,12 +1864,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="80" customHeight="1">
+    <row r="14" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -1864,7 +1903,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
@@ -1881,7 +1920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
@@ -1898,7 +1937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="80" customHeight="1">
+    <row r="17" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
@@ -1917,30 +1956,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="29.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="38.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="50.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="46.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="6" width="50.7109375" customWidth="1"/>
+    <col min="7" max="7" width="46.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -1963,7 +2001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
+    <row r="4" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1982,7 +2020,7 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2039,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2058,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" ht="48" customHeight="1">
+    <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2077,7 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2058,7 +2096,7 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2077,7 +2115,7 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2136,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2157,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2138,7 +2176,7 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" ht="48" customHeight="1">
+    <row r="13" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2159,7 +2197,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -2178,7 +2216,7 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
@@ -2199,7 +2237,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
@@ -2218,7 +2256,7 @@
       </c>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2275,7 @@
       </c>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -2258,7 +2296,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2315,7 @@
       </c>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" ht="48" customHeight="1">
+    <row r="20" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -2298,7 +2336,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="21" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -2317,7 +2355,7 @@
       </c>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
@@ -2338,7 +2376,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
@@ -2357,7 +2395,7 @@
       </c>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" ht="48" customHeight="1">
+    <row r="24" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
@@ -2376,7 +2414,7 @@
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" ht="48" customHeight="1">
+    <row r="25" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -2395,7 +2433,7 @@
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -2416,7 +2454,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
+    <row r="27" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -2437,7 +2475,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
+    <row r="28" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>23</v>
       </c>
@@ -2460,38 +2498,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="34.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="34.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="42.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="3" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="10" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>141</v>
       </c>
@@ -2505,7 +2537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>58</v>
       </c>
@@ -2517,7 +2549,7 @@
       </c>
       <c r="D5" s="5"/>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>61</v>
       </c>
@@ -2529,7 +2561,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>64</v>
       </c>
@@ -2541,7 +2573,7 @@
       </c>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>67</v>
       </c>
@@ -2553,7 +2585,7 @@
       </c>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
@@ -2565,7 +2597,7 @@
       </c>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>73</v>
       </c>
@@ -2577,7 +2609,7 @@
       </c>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -2591,7 +2623,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>80</v>
       </c>
@@ -2605,7 +2637,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>84</v>
       </c>
@@ -2617,7 +2649,7 @@
       </c>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>87</v>
       </c>
@@ -2631,12 +2663,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>143</v>
       </c>
@@ -2653,80 +2685,80 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="5">
         <v>1</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>0.797518473313863</v>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="C19" s="5">
+        <v>0.79751847331386305</v>
+      </c>
+      <c r="D19" s="5">
         <v>0.699283935466114</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>0.523589603649578</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+      <c r="E19" s="5">
+        <v>0.52358960364957796</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>0.797518473313863</v>
-      </c>
-      <c r="C20" s="5" t="n">
+      <c r="B20" s="5">
+        <v>0.79751847331386305</v>
+      </c>
+      <c r="C20" s="5">
         <v>1</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>0.900612729376448</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.686088094564509</v>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+      <c r="D20" s="5">
+        <v>0.90061272937644798</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.68608809456450903</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="5">
         <v>0.699283935466114</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>0.900612729376448</v>
-      </c>
-      <c r="D21" s="5" t="n">
+      <c r="C21" s="5">
+        <v>0.90061272937644798</v>
+      </c>
+      <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>0.596806665688881</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+      <c r="E21" s="5">
+        <v>0.59680666568888097</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>0.523589603649578</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0.686088094564509</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>0.596806665688881</v>
-      </c>
-      <c r="E22" s="5" t="n">
+      <c r="B22" s="5">
+        <v>0.52358960364957796</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.68608809456450903</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.59680666568888097</v>
+      </c>
+      <c r="E22" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>143</v>
       </c>
@@ -2737,56 +2769,56 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>0.744371722167872</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0.889169152951524</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+      <c r="B27" s="5">
+        <v>0.74437172216787195</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.88916915295152399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>0.925301095838809</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>0.822223870617545</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+      <c r="B28" s="5">
+        <v>0.92530109583880904</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.82222387061754498</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>0.829423586742266</v>
-      </c>
-      <c r="C29" s="5" t="n">
+      <c r="B29" s="5">
+        <v>0.82942358674226602</v>
+      </c>
+      <c r="C29" s="5">
         <v>0.858461890935584</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>0.647039621002448</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>0.922694293463358</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="B30" s="5">
+        <v>0.64703962100244805</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.92269429346335796</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>152</v>
       </c>
@@ -2812,64 +2844,64 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="5">
         <v>170</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="5">
         <v>4.8</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>0.436500337203419</v>
-      </c>
-      <c r="E35" s="5" t="n">
+      <c r="D35" s="5">
+        <v>0.43650033720341902</v>
+      </c>
+      <c r="E35" s="5">
         <v>2.25</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="5">
         <v>5</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="5">
         <v>121</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>71.1764705882353</v>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+      <c r="H35" s="5">
+        <v>71.176470588235304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="5">
         <v>170</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>4.79019607843137</v>
-      </c>
-      <c r="D36" s="5" t="n">
+      <c r="C36" s="5">
+        <v>4.7901960784313697</v>
+      </c>
+      <c r="D36" s="5">
         <v>0.433365907724587</v>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>2.33333333333333</v>
-      </c>
-      <c r="F36" s="5" t="n">
+      <c r="E36" s="5">
+        <v>2.3333333333333299</v>
+      </c>
+      <c r="F36" s="5">
         <v>5</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="5">
         <v>121</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>71.1764705882353</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="H36" s="5">
+        <v>71.176470588235304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>163</v>
       </c>
@@ -2877,7 +2909,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>164</v>
       </c>
@@ -2885,7 +2917,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>166</v>
       </c>
@@ -2893,7 +2925,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>168</v>
       </c>
@@ -2901,7 +2933,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>170</v>
       </c>
@@ -2909,7 +2941,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>172</v>
       </c>
@@ -2917,7 +2949,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>174</v>
       </c>
@@ -2925,7 +2957,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2933,7 +2965,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2941,7 +2973,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2949,7 +2981,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>180</v>
       </c>
@@ -2957,7 +2989,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>181</v>
       </c>
@@ -2965,7 +2997,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>183</v>
       </c>
@@ -2973,7 +3005,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>185</v>
       </c>
@@ -2981,7 +3013,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>187</v>
       </c>
@@ -2989,7 +3021,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>189</v>
       </c>
@@ -2999,39 +3031,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I67"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="34.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="11" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -3042,7 +3067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>91</v>
       </c>
@@ -3053,7 +3078,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -3064,7 +3089,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>98</v>
       </c>
@@ -3075,7 +3100,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>101</v>
       </c>
@@ -3086,7 +3111,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>104</v>
       </c>
@@ -3097,12 +3122,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>195</v>
       </c>
@@ -3131,41 +3156,41 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="5">
         <v>170</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="5">
         <v>10</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>-193.164823644255</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>406.32964728851</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>437.687631659012</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.0000000327028762958648</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="D14" s="5">
+        <v>-193.16482364425499</v>
+      </c>
+      <c r="E14" s="5">
+        <v>406.32964728850999</v>
+      </c>
+      <c r="F14" s="5">
+        <v>437.68763165901203</v>
+      </c>
+      <c r="G14" s="5">
+        <v>3.2702876295864802E-8</v>
+      </c>
+      <c r="H14" s="5">
         <v>1301.31627807825</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>207</v>
       </c>
@@ -3194,128 +3219,128 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>215</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>4.80725066991757</v>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="C19" s="5">
+        <v>4.8072506699175701</v>
+      </c>
+      <c r="D19" s="5">
         <v>1.97850804623326</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>2.42973521339463</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.0151098570885287</v>
+      <c r="E19" s="5">
+        <v>2.4297352133946299</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1.5109857088528701E-2</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="H19" s="5" t="n">
-        <v>0.929446156177672</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>8.68505518365747</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+      <c r="H19" s="5">
+        <v>0.92944615617767201</v>
+      </c>
+      <c r="I19" s="5">
+        <v>8.6850551836574699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>218</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>1.35117821863949</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0.360047523348167</v>
-      </c>
-      <c r="E20" s="5" t="n">
+      <c r="C20" s="5">
+        <v>1.3511782186394901</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.36004752334816698</v>
+      </c>
+      <c r="E20" s="5">
         <v>3.75277742803106</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>0.0001748861191692</v>
+      <c r="F20" s="5">
+        <v>1.748861191692E-4</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>0.645498040154237</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>2.05685839712474</v>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+      <c r="H20" s="5">
+        <v>0.64549804015423695</v>
+      </c>
+      <c r="I20" s="5">
+        <v>2.0568583971247398</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>220</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>0.669360047618217</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0.25433623691395</v>
-      </c>
-      <c r="E21" s="5" t="n">
+      <c r="C21" s="5">
+        <v>0.66936004761821699</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.25433623691395002</v>
+      </c>
+      <c r="E21" s="5">
         <v>2.63179189776517</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>0.00849358702296084</v>
+      <c r="F21" s="5">
+        <v>8.4935870229608402E-3</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>0.170870183303427</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>1.16784991193301</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+      <c r="H21" s="5">
+        <v>0.17087018330342699</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1.1678499119330099</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>222</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>0.258170986717962</v>
-      </c>
-      <c r="D22" s="5" t="n">
+      <c r="C22" s="5">
+        <v>0.25817098671796201</v>
+      </c>
+      <c r="D22" s="5">
         <v>0.119985187009894</v>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>2.1516904974001</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.0314217390711554</v>
+      <c r="E22" s="5">
+        <v>2.1516904974001001</v>
+      </c>
+      <c r="F22" s="5">
+        <v>3.1421739071155398E-2</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>0.0230043415002672</v>
-      </c>
-      <c r="I22" s="5" t="n">
+      <c r="H22" s="5">
+        <v>2.30043415002672E-2</v>
+      </c>
+      <c r="I22" s="5">
         <v>0.493337631935657</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>226</v>
       </c>
@@ -3335,72 +3360,72 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="5" t="n">
+    <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>0.486435719798699</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0.0755425806688728</v>
-      </c>
-      <c r="E27" s="5" t="n">
+      <c r="C27" s="5">
+        <v>0.48643571979869898</v>
+      </c>
+      <c r="D27" s="5">
+        <v>7.5542580668872802E-2</v>
+      </c>
+      <c r="E27" s="5">
         <v>0.338374982388497</v>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0.634496457208902</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="F27" s="5">
+        <v>0.63449645720890202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <v>0.71754824601539</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>0.0397243782606176</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0.639689895316334</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.795406596714447</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="C28" s="5">
+        <v>0.71754824601539002</v>
+      </c>
+      <c r="D28" s="5">
+        <v>3.9724378260617602E-2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.63968989531633402</v>
+      </c>
+      <c r="F28" s="5">
+        <v>0.79540659671444702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>0.821856109664551</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0.0335842912813252</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.756032108306851</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.887680111022251</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C29" s="5">
+        <v>0.82185610966455103</v>
+      </c>
+      <c r="D29" s="5">
+        <v>3.3584291281325201E-2</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.75603210830685097</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0.88768011102225097</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>233</v>
       </c>
@@ -3429,447 +3454,447 @@
         <v>165</v>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="5" t="n">
+    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>-1.6</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="5">
         <v>0</v>
       </c>
-      <c r="C34" s="5" t="n">
-        <v>0.287309943045396</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.082049349124095</v>
+      <c r="C34" s="5">
+        <v>0.28730994304539598</v>
+      </c>
+      <c r="D34" s="5">
+        <v>8.2049349124095006E-2</v>
       </c>
       <c r="E34" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>0.126496173807216</v>
-      </c>
-      <c r="G34" s="5" t="n">
+      <c r="F34" s="5">
+        <v>0.12649617380721601</v>
+      </c>
+      <c r="G34" s="5">
         <v>0.448123712283575</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I34" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="B35" s="5" t="n">
+    <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="B35" s="5">
         <v>0</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>0.342353092292042</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0.0798027581987172</v>
+      <c r="C35" s="5">
+        <v>0.34235309229204203</v>
+      </c>
+      <c r="D35" s="5">
+        <v>7.9802758198717197E-2</v>
       </c>
       <c r="E35" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="5">
         <v>0.185942560355598</v>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>0.498763624228486</v>
+      <c r="G35" s="5">
+        <v>0.49876362422848602</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I35" s="5">
         <v>4.25</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="n">
+    <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
         <v>-0.6</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="5">
         <v>0</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>0.404614215458542</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0.0763840262279075</v>
+      <c r="C36" s="5">
+        <v>0.40461421545854198</v>
+      </c>
+      <c r="D36" s="5">
+        <v>7.6384026227907506E-2</v>
       </c>
       <c r="E36" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.254904275057681</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.554324155859404</v>
+      <c r="F36" s="5">
+        <v>0.25490427505768098</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0.55432415585940398</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I36" s="5">
         <v>4.5</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>-0.0999999999999996</v>
-      </c>
-      <c r="B37" s="5" t="n">
+    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>-9.9999999999999603E-2</v>
+      </c>
+      <c r="B37" s="5">
         <v>0</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="5">
         <v>0.472417077245325</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>0.0751991963203096</v>
+      <c r="D37" s="5">
+        <v>7.5199196320309594E-2</v>
       </c>
       <c r="E37" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>0.325029360791162</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.619804793699489</v>
+      <c r="F37" s="5">
+        <v>0.32502936079116201</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0.61980479369948904</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I37" s="5">
         <v>4.75</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="5" t="n">
+    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>0.4</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="5">
         <v>0</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="5">
         <v>0.54328007762816</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>0.0792274193346424</v>
+      <c r="D38" s="5">
+        <v>7.9227419334642404E-2</v>
       </c>
       <c r="E38" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="5">
         <v>0.387997189144208</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>0.698562966112111</v>
+      <c r="G38" s="5">
+        <v>0.69856296611211099</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I38" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="5" t="n">
+    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
         <v>-1.6</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="5">
         <v>1</v>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>0.544121546078222</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0.0750244925944746</v>
+      <c r="C39" s="5">
+        <v>0.54412154607822205</v>
+      </c>
+      <c r="D39" s="5">
+        <v>7.5024492594474607E-2</v>
       </c>
       <c r="E39" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>0.39707624263466</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.691166849521784</v>
+      <c r="F39" s="5">
+        <v>0.39707624263466001</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0.69116684952178398</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I39" s="5" t="n">
+      <c r="I39" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="5" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="B40" s="5" t="n">
+    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="B40" s="5">
         <v>1</v>
       </c>
-      <c r="C40" s="5" t="n">
-        <v>0.600877419133603</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>0.0594253571827656</v>
+      <c r="C40" s="5">
+        <v>0.60087741913360304</v>
+      </c>
+      <c r="D40" s="5">
+        <v>5.9425357182765599E-2</v>
       </c>
       <c r="E40" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>0.484405859286954</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.717348978980253</v>
+      <c r="F40" s="5">
+        <v>0.48440585928695401</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0.71734897898025296</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40" s="5">
         <v>4.25</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="5" t="n">
+    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
         <v>-0.6</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>0.655871136833201</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0.0468319873965217</v>
+      <c r="C41" s="5">
+        <v>0.65587113683320097</v>
+      </c>
+      <c r="D41" s="5">
+        <v>4.6831987396521703E-2</v>
       </c>
       <c r="E41" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.564082128211585</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.747660145454818</v>
+      <c r="F41" s="5">
+        <v>0.56408212821158499</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0.74766014545481796</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I41" s="5">
         <v>4.5</v>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>-0.0999999999999996</v>
-      </c>
-      <c r="B42" s="5" t="n">
+    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>-9.9999999999999603E-2</v>
+      </c>
+      <c r="B42" s="5">
         <v>1</v>
       </c>
-      <c r="C42" s="5" t="n">
-        <v>0.707675743956906</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>0.0402166036320298</v>
+      <c r="C42" s="5">
+        <v>0.70767574395690602</v>
+      </c>
+      <c r="D42" s="5">
+        <v>4.02166036320298E-2</v>
       </c>
       <c r="E42" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.628852649257605</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.786498838656207</v>
+      <c r="F42" s="5">
+        <v>0.62885264925760498</v>
+      </c>
+      <c r="G42" s="5">
+        <v>0.78649883865620696</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="5">
         <v>4.75</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="5" t="n">
+    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>0.4</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="5">
         <v>1</v>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>0.755162980844954</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0.0399896011342091</v>
+      <c r="C43" s="5">
+        <v>0.75516298084495403</v>
+      </c>
+      <c r="D43" s="5">
+        <v>3.9989601134209102E-2</v>
       </c>
       <c r="E43" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>0.676784802865783</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.833541158824126</v>
+      <c r="F43" s="5">
+        <v>0.67678480286578302</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0.83354115882412605</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I43" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="5" t="n">
+    <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>-1.6</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="5">
         <v>2</v>
       </c>
-      <c r="C44" s="5" t="n">
-        <v>0.714216202542404</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>0.0581597386858782</v>
+      <c r="C44" s="5">
+        <v>0.71421620254240403</v>
+      </c>
+      <c r="D44" s="5">
+        <v>5.8159738685878197E-2</v>
       </c>
       <c r="E44" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.600225209367822</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.828207195716986</v>
+      <c r="F44" s="5">
+        <v>0.60022520936782198</v>
+      </c>
+      <c r="G44" s="5">
+        <v>0.82820719571698598</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I44" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="B45" s="5" t="n">
+    <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="B45" s="5">
         <v>2</v>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>0.751412321810927</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0.0466068363551617</v>
+      <c r="C45" s="5">
+        <v>0.75141232181092699</v>
+      </c>
+      <c r="D45" s="5">
+        <v>4.6606836355161697E-2</v>
       </c>
       <c r="E45" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.660064601121458</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.842760042500396</v>
+      <c r="F45" s="5">
+        <v>0.66006460112145804</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0.84276004250039604</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I45" s="5">
         <v>4.25</v>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="5" t="n">
+    <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
         <v>-0.6</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="5">
         <v>2</v>
       </c>
-      <c r="C46" s="5" t="n">
-        <v>0.785440365414206</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>0.0385245715667179</v>
+      <c r="C46" s="5">
+        <v>0.78544036541420603</v>
+      </c>
+      <c r="D46" s="5">
+        <v>3.8524571566717902E-2</v>
       </c>
       <c r="E46" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="5">
         <v>0.709933592623603</v>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>0.860947138204809</v>
+      <c r="G46" s="5">
+        <v>0.86094713820480895</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="I46" s="5">
         <v>4.5</v>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>-0.0999999999999996</v>
-      </c>
-      <c r="B47" s="5" t="n">
+    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>-9.9999999999999603E-2</v>
+      </c>
+      <c r="B47" s="5">
         <v>2</v>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>0.816125448314278</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0.0340878822530611</v>
+      <c r="C47" s="5">
+        <v>0.81612544831427802</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3.40878822530611E-2</v>
       </c>
       <c r="E47" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>0.749314426789036</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.882936469839519</v>
+      <c r="F47" s="5">
+        <v>0.74931442678903604</v>
+      </c>
+      <c r="G47" s="5">
+        <v>0.88293646983951901</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="5">
         <v>4.75</v>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="5" t="n">
+    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
         <v>0.4</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="5">
         <v>2</v>
       </c>
-      <c r="C48" s="5" t="n">
-        <v>0.843434034999438</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>0.0325105317671684</v>
+      <c r="C48" s="5">
+        <v>0.84343403499943803</v>
+      </c>
+      <c r="D48" s="5">
+        <v>3.25105317671684E-2</v>
       </c>
       <c r="E48" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>0.779714563617543</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.907153506381334</v>
+      <c r="F48" s="5">
+        <v>0.77971456361754299</v>
+      </c>
+      <c r="G48" s="5">
+        <v>0.90715350638133396</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="I48" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>163</v>
       </c>
@@ -3877,7 +3902,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>237</v>
       </c>
@@ -3885,7 +3910,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>239</v>
       </c>
@@ -3893,7 +3918,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>241</v>
       </c>
@@ -3901,7 +3926,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>243</v>
       </c>
@@ -3909,7 +3934,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
+    <row r="57" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>245</v>
       </c>
@@ -3917,7 +3942,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
+    <row r="58" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>247</v>
       </c>
@@ -3925,7 +3950,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>249</v>
       </c>
@@ -3933,7 +3958,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>251</v>
       </c>
@@ -3941,7 +3966,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>253</v>
       </c>
@@ -3949,7 +3974,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
+    <row r="62" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>255</v>
       </c>
@@ -3957,7 +3982,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>257</v>
       </c>
@@ -3965,7 +3990,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
+    <row r="64" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>259</v>
       </c>
@@ -3973,7 +3998,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>261</v>
       </c>
@@ -3981,7 +4006,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>263</v>
       </c>
@@ -3989,7 +4014,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
+    <row r="67" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>265</v>
       </c>
@@ -3999,39 +4024,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="34.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="11" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -4042,7 +4060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>108</v>
       </c>
@@ -4053,7 +4071,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -4064,7 +4082,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>114</v>
       </c>
@@ -4075,7 +4093,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>117</v>
       </c>
@@ -4086,7 +4104,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>121</v>
       </c>
@@ -4097,12 +4115,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>269</v>
       </c>
@@ -4113,67 +4131,67 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="5">
         <v>7</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>4.11764705882353</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="C14" s="5">
+        <v>4.1176470588235299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="5">
         <v>20</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>11.7647058823529</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="C15" s="5">
+        <v>11.764705882352899</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="5">
         <v>26</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>15.2941176470588</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="C16" s="5">
+        <v>15.294117647058799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="5">
         <v>55</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>32.3529411764706</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="C17" s="5">
+        <v>32.352941176470601</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="5">
         <v>62</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>36.4705882352941</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C18" s="5">
+        <v>36.470588235294102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>277</v>
       </c>
@@ -4208,47 +4226,47 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="5">
         <v>170</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="5">
         <v>10</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="5">
         <v>-169.61435196904</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>359.228703938081</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>390.586688308583</v>
-      </c>
-      <c r="G23" s="5" t="n">
+      <c r="E23" s="5">
+        <v>359.22870393808103</v>
+      </c>
+      <c r="F23" s="5">
+        <v>390.58668830858301</v>
+      </c>
+      <c r="G23" s="5">
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0.00000000000321342952247505</v>
-      </c>
-      <c r="J23" s="5" t="n">
+      <c r="I23" s="5">
+        <v>3.2134295224750499E-12</v>
+      </c>
+      <c r="J23" s="5">
         <v>38408.2228436937</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>207</v>
       </c>
@@ -4271,58 +4289,58 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>283</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <v>3.67736422710818</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1.04566860402294</v>
-      </c>
-      <c r="E28" s="5" t="n">
+      <c r="C28" s="5">
+        <v>3.6773642271081801</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1.0456686040229399</v>
+      </c>
+      <c r="E28" s="5">
         <v>3.51675876368523</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>0.000436850616945304</v>
+      <c r="F28" s="5">
+        <v>4.36850616945304E-4</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>284</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="5">
         <v>0.271512289987278</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>0.0963889737918388</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>2.816839720419</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.00484987218551836</v>
+      <c r="D29" s="5">
+        <v>9.6388973791838806E-2</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2.8168397204189999</v>
+      </c>
+      <c r="F29" s="5">
+        <v>4.8498721855183601E-3</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>287</v>
       </c>
@@ -4354,172 +4372,172 @@
         <v>291</v>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="5" t="n">
+    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C34" s="5" t="n">
-        <v>0.0108715978052725</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.0280842733017592</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>-0.0441725663981553</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.0659157620087003</v>
-      </c>
-      <c r="G34" s="5" t="n">
+      <c r="C34" s="5">
+        <v>1.08715978052725E-2</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2.8084273301759201E-2</v>
+      </c>
+      <c r="E34" s="5">
+        <v>-4.4172566398155297E-2</v>
+      </c>
+      <c r="F34" s="5">
+        <v>6.5915762008700293E-2</v>
+      </c>
+      <c r="G34" s="5">
         <v>0</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>0.0659157620087003</v>
-      </c>
-      <c r="I34" s="5" t="n">
+      <c r="H34" s="5">
+        <v>6.5915762008700293E-2</v>
+      </c>
+      <c r="I34" s="5">
         <v>0.1059157620087</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="n">
+    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>0.0962564548002007</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0.0399685883663237</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.0179194610892996</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0.174593448511102</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0179194610892996</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>0.174593448511102</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.214593448511102</v>
+      <c r="C35" s="5">
+        <v>9.6256454800200703E-2</v>
+      </c>
+      <c r="D35" s="5">
+        <v>3.99685883663237E-2</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1.79194610892996E-2</v>
+      </c>
+      <c r="F35" s="5">
+        <v>0.17459344851110201</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1.79194610892996E-2</v>
+      </c>
+      <c r="H35" s="5">
+        <v>0.17459344851110201</v>
+      </c>
+      <c r="I35" s="5">
+        <v>0.21459344851110199</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="n">
+    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
         <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>0.418243190948039</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0.0621931511094903</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0.296346854688381</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.540139527207697</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.296346854688381</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0.540139527207697</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0.580139527207697</v>
+      <c r="C36" s="5">
+        <v>0.41824319094803902</v>
+      </c>
+      <c r="D36" s="5">
+        <v>6.2193151109490301E-2</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.29634685468838101</v>
+      </c>
+      <c r="F36" s="5">
+        <v>0.54013952720769698</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0.29634685468838101</v>
+      </c>
+      <c r="H36" s="5">
+        <v>0.54013952720769698</v>
+      </c>
+      <c r="I36" s="5">
+        <v>0.58013952720769701</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="n">
+    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
         <v>3</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0.786640213005326</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0.0361421351876414</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.715802929713171</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0.857477496297481</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.715802929713171</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>0.857477496297481</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>0.897477496297481</v>
+      <c r="C37" s="5">
+        <v>0.78664021300532605</v>
+      </c>
+      <c r="D37" s="5">
+        <v>3.6142135187641401E-2</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.71580292971317105</v>
+      </c>
+      <c r="F37" s="5">
+        <v>0.85747749629748105</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0.71580292971317105</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0.85747749629748105</v>
+      </c>
+      <c r="I37" s="5">
+        <v>0.89747749629748097</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="5" t="n">
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>4</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C38" s="5" t="n">
-        <v>0.903839679639361</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0.0294415655543733</v>
-      </c>
-      <c r="E38" s="5" t="n">
+      <c r="C38" s="5">
+        <v>0.90383967963936096</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2.94415655543733E-2</v>
+      </c>
+      <c r="E38" s="5">
         <v>0.846135271504315</v>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>0.961544087774408</v>
-      </c>
-      <c r="G38" s="5" t="n">
+      <c r="F38" s="5">
+        <v>0.96154408777440803</v>
+      </c>
+      <c r="G38" s="5">
         <v>0.846135271504315</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>0.961544087774408</v>
-      </c>
-      <c r="I38" s="5" t="n">
+      <c r="H38" s="5">
+        <v>0.96154408777440803</v>
+      </c>
+      <c r="I38" s="5">
         <v>1.00154408777441</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>298</v>
       </c>
@@ -4539,46 +4557,46 @@
         <v>301</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="5" t="n">
+    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>9</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>365.336775984088</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>-173.668387992044</v>
+      <c r="B43" s="5">
+        <v>365.33677598408798</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-173.66838799204399</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="5" t="n">
+    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>10</v>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>359.228703938081</v>
-      </c>
-      <c r="C44" s="5" t="n">
+      <c r="B44" s="5">
+        <v>359.22870393808103</v>
+      </c>
+      <c r="C44" s="5">
         <v>-169.61435196904</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>8.10807204600752</v>
-      </c>
-      <c r="E44" s="5" t="n">
+      <c r="D44" s="5">
+        <v>8.1080720460075195</v>
+      </c>
+      <c r="E44" s="5">
         <v>1</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.0044068572179397</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="F44" s="5">
+        <v>4.4068572179397003E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>298</v>
       </c>
@@ -4598,76 +4616,68 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="5" t="n">
+    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
         <v>10</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>359.228703938081</v>
-      </c>
-      <c r="C49" s="5" t="n">
+      <c r="B49" s="5">
+        <v>359.22870393808103</v>
+      </c>
+      <c r="C49" s="5">
         <v>-169.61435196904</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="5" t="n">
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
         <v>11</v>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>361.217894003935</v>
-      </c>
-      <c r="C50" s="5" t="n">
+      <c r="B50" s="5">
+        <v>361.21789400393499</v>
+      </c>
+      <c r="C50" s="5">
         <v>-169.608947001968</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>0.0108099341450725</v>
-      </c>
-      <c r="E50" s="5" t="n">
+      <c r="D50" s="5">
+        <v>1.0809934145072499E-2</v>
+      </c>
+      <c r="E50" s="5">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.917192494874783</v>
+      <c r="F50" s="5">
+        <v>0.91719249487478305</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="39.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="36.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="24.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="24.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="24.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="24.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="24.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="24.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="4" max="12" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -4678,7 +4688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>124</v>
       </c>
@@ -4689,7 +4699,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>127</v>
       </c>
@@ -4700,7 +4710,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -4711,7 +4721,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -4722,7 +4732,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>135</v>
       </c>
@@ -4733,12 +4743,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>305</v>
       </c>
@@ -4752,68 +4762,68 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="5">
         <v>66</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>39.0532544378698</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="C14" s="5">
+        <v>39.053254437869803</v>
+      </c>
+      <c r="D14" s="5">
         <v>169</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="5">
         <v>45</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>26.6272189349112</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="C15" s="5">
+        <v>26.627218934911198</v>
+      </c>
+      <c r="D15" s="5">
         <v>169</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="5">
         <v>28</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>16.5680473372781</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="C16" s="5">
+        <v>16.568047337278099</v>
+      </c>
+      <c r="D16" s="5">
         <v>169</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="5">
         <v>30</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="5">
         <v>17.7514792899408</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="5">
         <v>169</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>55</v>
       </c>
@@ -4827,138 +4837,138 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="5">
         <v>169</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="5">
         <v>169</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="5">
         <v>139</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="5">
         <v>169</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>82.2485207100592</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="D23" s="5">
+        <v>82.248520710059196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="5">
         <v>30</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="5">
         <v>169</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="5">
         <v>17.7514792899408</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="5">
         <v>111</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="5">
         <v>169</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>65.6804733727811</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+      <c r="D25" s="5">
+        <v>65.680473372781094</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="5">
         <v>28</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="5">
         <v>169</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>16.5680473372781</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+      <c r="D26" s="5">
+        <v>16.568047337278099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="5">
         <v>66</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="5">
         <v>169</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>39.0532544378698</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+      <c r="D27" s="5">
+        <v>39.053254437869803</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="5">
         <v>45</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="5">
         <v>169</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>26.6272189349112</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+      <c r="D28" s="5">
+        <v>26.627218934911198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="5">
         <v>111</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="5">
         <v>139</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>79.8561151079137</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+      <c r="D29" s="5">
+        <v>79.856115107913695</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="5">
         <v>66</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="5">
         <v>111</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>59.4594594594595</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="D30" s="5">
+        <v>59.459459459459502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -4990,44 +5000,44 @@
         <v>324</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>325</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="5">
         <v>169</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="5">
         <v>9</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>-197.778523876022</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>413.557047752043</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>441.726136186351</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>11.3466825882866</v>
-      </c>
-      <c r="I35" s="5" t="n">
+      <c r="E35" s="5">
+        <v>-197.77852387602201</v>
+      </c>
+      <c r="F35" s="5">
+        <v>413.55704775204299</v>
+      </c>
+      <c r="G35" s="5">
+        <v>441.72613618635103</v>
+      </c>
+      <c r="H35" s="5">
+        <v>11.346682588286599</v>
+      </c>
+      <c r="I35" s="5">
         <v>3</v>
       </c>
-      <c r="J35" s="5" t="n">
-        <v>0.00999161109243892</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="J35" s="5">
+        <v>9.9916110924389203E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>328</v>
       </c>
@@ -5059,7 +5069,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>307</v>
       </c>
@@ -5069,29 +5079,29 @@
       <c r="C40" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D40" s="5" t="n">
-        <v>0.760932342909135</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.20986644683436</v>
-      </c>
-      <c r="F40" s="5" t="n">
+      <c r="D40" s="5">
+        <v>0.76093234290913503</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0.20986644683436001</v>
+      </c>
+      <c r="F40" s="5">
         <v>3.62579323368309</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>0.00028807579294856</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>2.14027075682019</v>
-      </c>
-      <c r="I40" s="5" t="n">
+      <c r="G40" s="5">
+        <v>2.8807579294856E-4</v>
+      </c>
+      <c r="H40" s="5">
+        <v>2.1402707568201902</v>
+      </c>
+      <c r="I40" s="5">
         <v>1.41850239766936</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J40" s="5">
         <v>3.22929232973169</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>307</v>
       </c>
@@ -5101,29 +5111,29 @@
       <c r="C41" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>-0.311508217713151</v>
-      </c>
-      <c r="E41" s="5" t="n">
+      <c r="D41" s="5">
+        <v>-0.31150821771315101</v>
+      </c>
+      <c r="E41" s="5">
         <v>0.209833462173563</v>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>-1.48454976859453</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.137663130165508</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.732341592307507</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0.485403756702286</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>1.10490329013346</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+      <c r="F41" s="5">
+        <v>-1.4845497685945299</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0.13766313016550799</v>
+      </c>
+      <c r="H41" s="5">
+        <v>0.73234159230750695</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0.48540375670228603</v>
+      </c>
+      <c r="J41" s="5">
+        <v>1.1049032901334599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>308</v>
       </c>
@@ -5133,29 +5143,29 @@
       <c r="C42" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="5">
         <v>1.64579789150885</v>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>0.401144407357046</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>4.10275666648887</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0000408256558610201</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>5.18514544039462</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>2.36214310070562</v>
-      </c>
-      <c r="J42" s="5" t="n">
+      <c r="E42" s="5">
+        <v>0.40114440735704598</v>
+      </c>
+      <c r="F42" s="5">
+        <v>4.1027566664888697</v>
+      </c>
+      <c r="G42" s="5">
+        <v>4.0825655861020099E-5</v>
+      </c>
+      <c r="H42" s="5">
+        <v>5.1851454403946198</v>
+      </c>
+      <c r="I42" s="5">
+        <v>2.3621431007056199</v>
+      </c>
+      <c r="J42" s="5">
         <v>11.3819239952117</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>308</v>
       </c>
@@ -5165,29 +5175,29 @@
       <c r="C43" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0.960917478015536</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0.685014309869967</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1.40276993366451</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.160685455457465</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>2.61409374707551</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>0.682709459784585</v>
-      </c>
-      <c r="J43" s="5" t="n">
+      <c r="D43" s="5">
+        <v>0.96091747801553595</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.68501430986996703</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1.4027699336645101</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0.16068545545746499</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2.6140937470755099</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0.68270945978458497</v>
+      </c>
+      <c r="J43" s="5">
         <v>10.0093619922235</v>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>309</v>
       </c>
@@ -5197,29 +5207,29 @@
       <c r="C44" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>0.200617741115646</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.193820413243273</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>1.03507023722956</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.300636110876058</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>1.22215750195679</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0.835885791465132</v>
-      </c>
-      <c r="J44" s="5" t="n">
+      <c r="D44" s="5">
+        <v>0.20061774111564601</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.19382041324327301</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1.0350702372295599</v>
+      </c>
+      <c r="G44" s="5">
+        <v>0.30063611087605802</v>
+      </c>
+      <c r="H44" s="5">
+        <v>1.2221575019567901</v>
+      </c>
+      <c r="I44" s="5">
+        <v>0.83588579146513198</v>
+      </c>
+      <c r="J44" s="5">
         <v>1.78692947629982</v>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>309</v>
       </c>
@@ -5229,34 +5239,34 @@
       <c r="C45" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="5">
         <v>0.6758583758433</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>0.445300327280235</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="5">
         <v>1.51775854280469</v>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>0.129075279724774</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="G45" s="5">
+        <v>0.12907527972477401</v>
+      </c>
+      <c r="H45" s="5">
         <v>1.96571957819761</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>0.821261071554031</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>4.70502449701852</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="I45" s="5">
+        <v>0.82126107155403105</v>
+      </c>
+      <c r="J45" s="5">
+        <v>4.7050244970185204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>334</v>
       </c>
@@ -5282,64 +5292,64 @@
         <v>211</v>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="5">
         <v>169</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="5">
         <v>169</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>-203.451865170165</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>-197.778523876022</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>11.3466825882866</v>
-      </c>
-      <c r="G50" s="5" t="n">
+      <c r="D50" s="5">
+        <v>-203.45186517016501</v>
+      </c>
+      <c r="E50" s="5">
+        <v>-197.77852387602201</v>
+      </c>
+      <c r="F50" s="5">
+        <v>11.346682588286599</v>
+      </c>
+      <c r="G50" s="5">
         <v>3</v>
       </c>
-      <c r="H50" s="5" t="n">
-        <v>0.00999161109243892</v>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+      <c r="H50" s="5">
+        <v>9.9916110924389203E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="5">
         <v>169</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="5">
         <v>169</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>-216.388808449434</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>-197.778523876022</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>37.2205691468256</v>
-      </c>
-      <c r="G51" s="5" t="n">
+      <c r="D51" s="5">
+        <v>-216.38880844943401</v>
+      </c>
+      <c r="E51" s="5">
+        <v>-197.77852387602201</v>
+      </c>
+      <c r="F51" s="5">
+        <v>37.220569146825603</v>
+      </c>
+      <c r="G51" s="5">
         <v>3</v>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>0.000000041325511550435</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="H51" s="5">
+        <v>4.1325511550434999E-8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>332</v>
       </c>
@@ -5359,312 +5369,312 @@
         <v>345</v>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="n">
+    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
         <v>0</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="5">
         <v>7</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E56" s="5" t="n">
-        <v>0.748540098174989</v>
+      <c r="E56" s="5">
+        <v>0.74854009817498901</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="n">
+    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
         <v>0</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="5">
         <v>7</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E57" s="5" t="n">
-        <v>0.0596678850022681</v>
+      <c r="E57" s="5">
+        <v>5.9667885002268099E-2</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
+    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
         <v>0</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="5">
         <v>7</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>0.191792016822742</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="n">
+    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="5">
         <v>20</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>0.671513907273812</v>
+      <c r="E59" s="5">
+        <v>0.67151390727381199</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n">
+    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="5">
         <v>20</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>0.118206248954012</v>
+      <c r="E60" s="5">
+        <v>0.11820624895401199</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="5" t="n">
+    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="5">
         <v>20</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>0.210279843772176</v>
+      <c r="E61" s="5">
+        <v>0.21027984377217601</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
+    <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
         <v>2</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="5">
         <v>26</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>0.559414785467786</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n">
+    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
         <v>2</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="5">
         <v>26</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>0.226491581049719</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
+    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
         <v>2</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="5">
         <v>26</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>0.214093633482495</v>
+      <c r="E64" s="5">
+        <v>0.21409363348249499</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="5" t="n">
+    <row r="65" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
         <v>3</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="5">
         <v>55</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>0.403212329590995</v>
+      <c r="E65" s="5">
+        <v>0.40321232959099501</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n">
+    <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
         <v>3</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="5">
         <v>55</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>0.408192401539595</v>
+      <c r="E66" s="5">
+        <v>0.40819240153959502</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="5" t="n">
+    <row r="67" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
         <v>3</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="5">
         <v>55</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>0.18859526886941</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
+    <row r="68" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
         <v>4</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="5">
         <v>61</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>0.222498276990852</v>
+      <c r="E68" s="5">
+        <v>0.22249827699085201</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="5" t="n">
+    <row r="69" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
         <v>4</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="5">
         <v>61</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>0.650312351823314</v>
+      <c r="E69" s="5">
+        <v>0.65031235182331404</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="n">
+    <row r="70" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
         <v>4</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="5">
         <v>61</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>0.127189371185834</v>
+      <c r="E70" s="5">
+        <v>0.12718937118583401</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>328</v>
       </c>
@@ -5690,234 +5700,226 @@
         <v>369</v>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>307</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C75" s="5" t="n">
-        <v>0.760932342909135</v>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>0.726155291448061</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>2.14027075682019</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>2.06711784457618</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.0347770514610743</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>3.41792794257007</v>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+      <c r="C75" s="5">
+        <v>0.76093234290913503</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.72615529144806101</v>
+      </c>
+      <c r="E75" s="5">
+        <v>2.1402707568201902</v>
+      </c>
+      <c r="F75" s="5">
+        <v>2.0671178445761802</v>
+      </c>
+      <c r="G75" s="5">
+        <v>3.47770514610743E-2</v>
+      </c>
+      <c r="H75" s="5">
+        <v>3.4179279425700702</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>307</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="5" t="n">
-        <v>-0.311508217713151</v>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>-0.284433705455729</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>0.732341592307507</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.752440236493124</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.0270745122574225</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>2.74443571097597</v>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
+      <c r="C76" s="5">
+        <v>-0.31150821771315101</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-0.28443370545572899</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.73234159230750695</v>
+      </c>
+      <c r="F76" s="5">
+        <v>0.75244023649312397</v>
+      </c>
+      <c r="G76" s="5">
+        <v>2.7074512257422498E-2</v>
+      </c>
+      <c r="H76" s="5">
+        <v>2.7444357109759698</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="5">
         <v>1.64579789150885</v>
       </c>
-      <c r="D77" s="5" t="n">
-        <v>1.5536104009257</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>5.18514544039462</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>4.72851122288236</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.0921874905831499</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>8.80658455508057</v>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
+      <c r="D77" s="5">
+        <v>1.5536104009256999</v>
+      </c>
+      <c r="E77" s="5">
+        <v>5.1851454403946198</v>
+      </c>
+      <c r="F77" s="5">
+        <v>4.7285112228823598</v>
+      </c>
+      <c r="G77" s="5">
+        <v>9.21874905831499E-2</v>
+      </c>
+      <c r="H77" s="5">
+        <v>8.8065845550805708</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C78" s="5" t="n">
-        <v>0.960917478015536</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>0.730679170296978</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>2.61409374707551</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>2.07649041948365</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.230238307718558</v>
-      </c>
-      <c r="H78" s="5" t="n">
+      <c r="C78" s="5">
+        <v>0.96091747801553595</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0.73067917029697804</v>
+      </c>
+      <c r="E78" s="5">
+        <v>2.6140937470755099</v>
+      </c>
+      <c r="F78" s="5">
+        <v>2.0764904194836502</v>
+      </c>
+      <c r="G78" s="5">
+        <v>0.23023830771855799</v>
+      </c>
+      <c r="H78" s="5">
         <v>20.5655718427581</v>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C79" s="5" t="n">
-        <v>0.200617741115646</v>
-      </c>
-      <c r="D79" s="5" t="n">
+      <c r="C79" s="5">
+        <v>0.20061774111564601</v>
+      </c>
+      <c r="D79" s="5">
         <v>0.193368834225632</v>
       </c>
-      <c r="E79" s="5" t="n">
-        <v>1.22215750195679</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>1.21333022871468</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.00724890689001415</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0.722269693387967</v>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
+      <c r="E79" s="5">
+        <v>1.2221575019567901</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1.2133302287146801</v>
+      </c>
+      <c r="G79" s="5">
+        <v>7.2489068900141503E-3</v>
+      </c>
+      <c r="H79" s="5">
+        <v>0.72226969338796698</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="5">
         <v>0.6758583758433</v>
       </c>
-      <c r="D80" s="5" t="n">
-        <v>0.56022538931588</v>
-      </c>
-      <c r="E80" s="5" t="n">
+      <c r="D80" s="5">
+        <v>0.56022538931587995</v>
+      </c>
+      <c r="E80" s="5">
         <v>1.96571957819761</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="5">
         <v>1.751067127644</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="5">
         <v>0.11563298652742</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="5">
         <v>10.919790031823</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:A87"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="1" max="9" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>374</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="95.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="95.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>376</v>
       </c>
@@ -5934,7 +5936,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>381</v>
       </c>
@@ -5947,11 +5949,11 @@
       <c r="D4" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="5">
         <v>22.51</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>384</v>
       </c>
@@ -5964,11 +5966,11 @@
       <c r="D5" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>19.96</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>386</v>
       </c>
@@ -5981,11 +5983,11 @@
       <c r="D6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>13.35</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>388</v>
       </c>
@@ -5998,11 +6000,11 @@
       <c r="D7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>11.67</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>390</v>
       </c>
@@ -6015,11 +6017,11 @@
       <c r="D8" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>20.9</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>392</v>
       </c>
@@ -6032,11 +6034,11 @@
       <c r="D9" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>235.21</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>394</v>
       </c>
@@ -6049,11 +6051,11 @@
       <c r="D10" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>21.52</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>371</v>
       </c>
@@ -6066,11 +6068,11 @@
       <c r="D11" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>149.06</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>372</v>
       </c>
@@ -6083,11 +6085,11 @@
       <c r="D12" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>131.75</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>373</v>
       </c>
@@ -6100,11 +6102,11 @@
       <c r="D13" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>207.66</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>374</v>
       </c>
@@ -6117,12 +6119,12 @@
       <c r="D14" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="5">
         <v>368.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/output/learner_integrated_phase4A_4D/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
+++ b/output/learner_integrated_phase4A_4D/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
@@ -1,1242 +1,1235 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangpinyi\Desktop\Lastinger\assessment-feedback-analysis\output\learner_integrated_phase4A_4D\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B7D30B579F4B4CA8F1E4AA7282CE9C4D7D0EDAA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Headline Metrics" sheetId="2" r:id="rId2"/>
-    <sheet name="Phase 4A" sheetId="3" r:id="rId3"/>
-    <sheet name="Phase 4B" sheetId="4" r:id="rId4"/>
-    <sheet name="Phase 4C" sheetId="5" r:id="rId5"/>
-    <sheet name="Phase 4D" sheetId="6" r:id="rId6"/>
-    <sheet name="Figures" sheetId="7" r:id="rId7"/>
-    <sheet name="Sources" sheetId="8" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Headline Metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase 4A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phase 4B" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phase 4C" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Phase 4D" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Figures" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sources" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
-  <si>
-    <t>Learner Survey: Integrated Phase 4A-4D Results</t>
-  </si>
-  <si>
-    <t>The sequence from feedback experience to AI comfort, perceived usefulness, and preferred feedback model is an interpretive and associational synthesis, not a causal or mediation model.</t>
-  </si>
-  <si>
-    <t>Executive Summary</t>
-  </si>
-  <si>
-    <t>phase</t>
-  </si>
-  <si>
-    <t>analytic_focus</t>
-  </si>
-  <si>
-    <t>key_result</t>
-  </si>
-  <si>
-    <t>interpretation</t>
-  </si>
-  <si>
-    <t>reporting_caution</t>
-  </si>
-  <si>
-    <t>Phase 4A</t>
-  </si>
-  <si>
-    <t>Feedback-experience measurement</t>
-  </si>
-  <si>
-    <t>The four feedback items formed a strongly reliable ordinal index (ordinal alpha = 0.903). The composite mean was 4.80, and 71.2% received the maximum score.</t>
-  </si>
-  <si>
-    <t>The current feedback process provides a strong experiential foundation, but the severe ceiling effect limits differentiation among highly positive experiences.</t>
-  </si>
-  <si>
-    <t>The four-item CFA was inadmissible; the scale should be described as a reliable unit-weighted index rather than a confirmed latent factor.</t>
-  </si>
-  <si>
-    <t>Phase 4B</t>
-  </si>
-  <si>
-    <t>AI comfort</t>
-  </si>
-  <si>
-    <t>Greater AI comfort was associated with extensive prior AI experience, greater awareness of AI use, and more favorable feedback experience. Adjusted comfort probability increased from 48.6% among respondents not aware of AI use to 82.2% among fully aware respondents.</t>
-  </si>
-  <si>
-    <t>AI readiness corresponds with prior exposure, transparency, and learners' experiences of the feedback process.</t>
-  </si>
-  <si>
-    <t>AI awareness affected both the location and scale components of comfort, so adjusted probabilities are more interpretable than one proportional-odds ratio.</t>
-  </si>
-  <si>
-    <t>Phase 4C</t>
-  </si>
-  <si>
-    <t>Perceived AI usefulness</t>
-  </si>
-  <si>
-    <t>68.8% agreed that AI-generated feedback could be as useful as human feedback. Adjusted agreement increased from 1.1% to 90.4% across the AI-comfort scale.</t>
-  </si>
-  <si>
-    <t>AI comfort is the clearest bridge between general readiness and believing that AI-generated feedback is useful.</t>
-  </si>
-  <si>
-    <t>The selected location-scale model had an elevated Hessian condition number, so emphasis should remain on adjusted probabilities and the overall pattern.</t>
-  </si>
-  <si>
-    <t>Phase 4D</t>
-  </si>
-  <si>
-    <t>Preferred feedback model</t>
-  </si>
-  <si>
-    <t>65.7% preferred a model involving universal human review. The adjusted probability of an AI-forward model increased from 6.0% to 65.0% across perceived AI-usefulness levels.</t>
-  </si>
-  <si>
-    <t>Learners distinguish between viewing AI as useful and granting AI unrestricted responsibility for feedback or grading.</t>
-  </si>
-  <si>
-    <t>The multinomial analysis was associational, and sparse predictor-by-outcome cells warrant caution with individual category-specific estimates.</t>
-  </si>
-  <si>
-    <t>Cross-Phase Synthesis</t>
-  </si>
-  <si>
-    <t>evidence_stage</t>
-  </si>
-  <si>
-    <t>contributing_phases</t>
-  </si>
-  <si>
-    <t>main_evidence</t>
-  </si>
-  <si>
-    <t>integrated_interpretation</t>
-  </si>
-  <si>
-    <t>inference_boundary</t>
-  </si>
-  <si>
-    <t>1. Feedback foundation</t>
-  </si>
-  <si>
-    <t>Ordinal alpha = 0.903; composite mean = 4.80; maximum-score percentage = 71.2%.</t>
-  </si>
-  <si>
-    <t>Respondents evaluated the existing feedback process exceptionally positively, creating a favorable but compressed foundation for considering AI-supported feedback.</t>
-  </si>
-  <si>
-    <t>The scale findings describe measurement quality and response distribution; they do not establish causal effects.</t>
-  </si>
-  <si>
-    <t>2. Readiness for AI-supported feedback</t>
-  </si>
-  <si>
-    <t>Phases 4A and 4B</t>
-  </si>
-  <si>
-    <t>Extensive prior AI experience, AI awareness, and feedback experience were associated with AI comfort.</t>
-  </si>
-  <si>
-    <t>Comfort with AI appears connected to familiarity, transparency, and experience rather than functioning only as a fixed personal attitude.</t>
-  </si>
-  <si>
-    <t>The Phase 4B associations do not demonstrate that awareness or feedback experience causes comfort.</t>
-  </si>
-  <si>
-    <t>3. Perceived usefulness of AI feedback</t>
-  </si>
-  <si>
-    <t>Phases 4B and 4C</t>
-  </si>
-  <si>
-    <t>Adjusted agreement that AI feedback could be as useful as human feedback increased from 1.1% to 90.4% across AI-comfort levels.</t>
-  </si>
-  <si>
-    <t>Comfort is more proximally connected to perceived AI usefulness than the general feedback-experience index.</t>
-  </si>
-  <si>
-    <t>The sequence from comfort to usefulness is an analytic synthesis, not a tested mediation model.</t>
-  </si>
-  <si>
-    <t>4. Preferred implementation model</t>
-  </si>
-  <si>
-    <t>Phases 4C and 4D</t>
-  </si>
-  <si>
-    <t>65.7% preferred universal human review, while adjusted AI-forward preference increased from 6.0% to 65.0% across perceived usefulness levels.</t>
-  </si>
-  <si>
-    <t>Greater perceived usefulness corresponds with more AI-forward preferences, but learners continue to place substantial value on universal human review.</t>
-  </si>
-  <si>
-    <t>The preference results show associations and adjusted probabilities, not causal effects of usefulness on model choice.</t>
-  </si>
-  <si>
-    <t>Integrated Headline Metrics</t>
-  </si>
-  <si>
-    <t>domain</t>
-  </si>
-  <si>
-    <t>metric</t>
-  </si>
-  <si>
-    <t>estimate</t>
-  </si>
-  <si>
-    <t>statistical_evidence</t>
-  </si>
-  <si>
-    <t>Analytic sample</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>All 170 respondents had complete data for the four feedback items.</t>
-  </si>
-  <si>
-    <t>Ordinal alpha</t>
-  </si>
-  <si>
-    <t>0.903</t>
-  </si>
-  <si>
-    <t>The four-item index demonstrated strong ordinal reliability.</t>
-  </si>
-  <si>
-    <t>Average polychoric correlation</t>
-  </si>
-  <si>
-    <t>0.701</t>
-  </si>
-  <si>
-    <t>The feedback items were strongly related at the latent-response level.</t>
-  </si>
-  <si>
-    <t>Range of polychoric correlations</t>
-  </si>
-  <si>
-    <t>0.524 to 0.901</t>
-  </si>
-  <si>
-    <t>All item pairs were positively associated, although the strength varied across pairs.</t>
-  </si>
-  <si>
-    <t>Variance represented by first component</t>
-  </si>
-  <si>
-    <t>78.0%</t>
-  </si>
-  <si>
-    <t>A dominant first component supported summarizing the items with one overall feedback-experience score.</t>
-  </si>
-  <si>
-    <t>Feedback-experience composite mean</t>
-  </si>
-  <si>
-    <t>4.80</t>
-  </si>
-  <si>
-    <t>Learners reported exceptionally favorable feedback experiences.</t>
-  </si>
-  <si>
-    <t>Feedback-experience composite SD</t>
-  </si>
-  <si>
-    <t>0.437</t>
-  </si>
-  <si>
-    <t>The composite displayed limited variability.</t>
-  </si>
-  <si>
-    <t>Interpret regression estimates in light of the restricted score variation.</t>
-  </si>
-  <si>
-    <t>Maximum-score respondents</t>
-  </si>
-  <si>
-    <t>71.2%</t>
-  </si>
-  <si>
-    <t>The pronounced ceiling effect limits differentiation among respondents with very positive feedback experiences.</t>
-  </si>
-  <si>
-    <t>Do not treat the composite as finely distinguishing highly satisfied respondents.</t>
-  </si>
-  <si>
-    <t>Primary-sensitivity composite correlation</t>
-  </si>
-  <si>
-    <t>0.981</t>
-  </si>
-  <si>
-    <t>The four-item and three-item scores produced nearly identical respondent rankings.</t>
-  </si>
-  <si>
-    <t>Measurement decision</t>
-  </si>
-  <si>
-    <t>Retain the four-item unit-weighted index; do not interpret the inadmissible CFA.</t>
-  </si>
-  <si>
-    <t>The four-item index is retained for substantive coverage, with the three-item version used as a sensitivity measure.</t>
-  </si>
-  <si>
-    <t>Do not report CFA-based omega or global CFA fit because the four-item CFA was inadmissible.</t>
-  </si>
-  <si>
-    <t>Extensive prior AI experience</t>
-  </si>
-  <si>
-    <t>Location coefficient = 4.81, p = 0.015</t>
-  </si>
-  <si>
-    <t>Respondents with extensive prior AI experience reported greater comfort with AI-supported feedback.</t>
-  </si>
-  <si>
-    <t>AI awareness</t>
-  </si>
-  <si>
-    <t>Location coefficient = 1.35, p &lt; .001; log-scale coefficient = 0.258, p = 0.031</t>
-  </si>
-  <si>
-    <t>Greater awareness corresponded with higher comfort, but awareness also changed the dispersion of the latent comfort response.</t>
-  </si>
-  <si>
-    <t>Awareness affected both location and scale; use adjusted probabilities for interpretation.</t>
-  </si>
-  <si>
-    <t>Feedback experience</t>
-  </si>
-  <si>
-    <t>Location coefficient per 0.5-point increase = 0.669, p = 0.008</t>
-  </si>
-  <si>
-    <t>More favorable feedback experiences were associated with greater AI comfort.</t>
-  </si>
-  <si>
-    <t>Adjusted comfort probability by awareness</t>
-  </si>
-  <si>
-    <t>Probability of somewhat or strongly agreeing with AI comfort: 48.6% among respondents not aware of AI use, 71.8% among somewhat aware respondents, and 82.2% among fully aware respondents.</t>
-  </si>
-  <si>
-    <t>The adjusted probabilities show a substantial increase in comfort across awareness levels.</t>
-  </si>
-  <si>
-    <t>Model form</t>
-  </si>
-  <si>
-    <t>Cumulative-link location-scale model; AIC = 406.33.</t>
-  </si>
-  <si>
-    <t>Because awareness affected both location and scale, adjusted probabilities are preferable to a single proportional-odds ratio.</t>
-  </si>
-  <si>
-    <t>The Hessian condition number was elevated, so large individual coefficients should be interpreted cautiously.</t>
-  </si>
-  <si>
-    <t>Observed perceived usefulness</t>
-  </si>
-  <si>
-    <t>117 of 170 respondents (68.8%) somewhat or strongly agreed that AI-generated feedback could be as useful as human feedback.</t>
-  </si>
-  <si>
-    <t>A majority of respondents viewed AI-generated feedback as potentially comparable in usefulness to human feedback.</t>
-  </si>
-  <si>
-    <t>Location coefficient = 3.68, p &lt; .001; log-scale coefficient = 0.272, p = 0.005</t>
-  </si>
-  <si>
-    <t>AI comfort was strongly associated with perceived AI usefulness and also affected latent-response dispersion.</t>
-  </si>
-  <si>
-    <t>Comfort affected both location and scale; adjusted probabilities are the primary effect-size presentation.</t>
-  </si>
-  <si>
-    <t>Adjusted usefulness probability</t>
-  </si>
-  <si>
-    <t>Adjusted agreement probability increased from 1.1% at the lowest comfort level to 90.4% at the highest comfort level.</t>
-  </si>
-  <si>
-    <t>Comfort clearly distinguished respondents with low versus high adjusted probabilities of viewing AI feedback as useful.</t>
-  </si>
-  <si>
-    <t>Location-scale model improvement</t>
-  </si>
-  <si>
-    <t>Likelihood-ratio test p = 0.004; selected-model AIC = 359.23.</t>
-  </si>
-  <si>
-    <t>The location-scale model fit better than the proportional-odds benchmark.</t>
-  </si>
-  <si>
-    <t>The selected model had an elevated Hessian condition number.</t>
-  </si>
-  <si>
-    <t>Feedback-experience contribution</t>
-  </si>
-  <si>
-    <t>Adding feedback experience after AI comfort: likelihood-ratio test p = 0.917.</t>
-  </si>
-  <si>
-    <t>Feedback experience did not improve the usefulness model after AI comfort was included.</t>
-  </si>
-  <si>
-    <t>Largest preferred-model category</t>
-  </si>
-  <si>
-    <t>Human-led grading with AI support: 66 of 169 respondents (39.1%).</t>
-  </si>
-  <si>
-    <t>The most common single preference retained instructor control and used AI only as a support tool.</t>
-  </si>
-  <si>
-    <t>Universal human review</t>
-  </si>
-  <si>
-    <t>111 of 169 respondents (65.7%) preferred universal human review. Among respondents with a directional preference, the percentage was 79.9%.</t>
-  </si>
-  <si>
-    <t>Learners generally accepted AI assistance while retaining a strong preference for universal human accountability.</t>
-  </si>
-  <si>
-    <t>Adding perceived usefulness to a feedback-only model: likelihood-ratio test p &lt; .001.</t>
-  </si>
-  <si>
-    <t>Perceived AI usefulness substantially distinguished preferred feedback models.</t>
-  </si>
-  <si>
-    <t>Interpret omnibus likelihood-ratio tests alongside category-specific coefficients.</t>
-  </si>
-  <si>
-    <t>Adding feedback experience to a usefulness-only model: likelihood-ratio test p = 0.010.</t>
-  </si>
-  <si>
-    <t>Feedback experience improved overall model fit even though its individual category-specific Wald coefficients were not statistically significant.</t>
-  </si>
-  <si>
-    <t>Adjusted AI-forward preference</t>
-  </si>
-  <si>
-    <t>Adjusted probability of an AI-forward feedback model increased from 6.0% among respondents who strongly disagreed that AI feedback was as useful as human feedback to 65.0% among those who strongly agreed.</t>
-  </si>
-  <si>
-    <t>More favorable perceptions of AI usefulness corresponded with substantially more AI-forward implementation preferences.</t>
-  </si>
-  <si>
-    <t>The results are associational, and some predictor-by-outcome cells were sparse.</t>
-  </si>
-  <si>
-    <t>Phase 4A: Feedback-Experience Scale Diagnostics</t>
-  </si>
-  <si>
-    <t>Headline Results</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>Polychoric Correlation Matrix</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>rubric_clear_aligned</t>
-  </si>
-  <si>
-    <t>feedback_specific_relevant</t>
-  </si>
-  <si>
-    <t>feedback_helped_improve</t>
-  </si>
-  <si>
-    <t>feedback_timely</t>
-  </si>
-  <si>
-    <t>Ordinal Item Diagnostics</t>
-  </si>
-  <si>
-    <t>ordinal_item_rest_correlation</t>
-  </si>
-  <si>
-    <t>ordinal_alpha_if_deleted</t>
-  </si>
-  <si>
-    <t>Composite Summary</t>
-  </si>
-  <si>
-    <t>composite</t>
-  </si>
-  <si>
-    <t>valid_n</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>standard_deviation</t>
-  </si>
-  <si>
-    <t>minimum</t>
-  </si>
-  <si>
-    <t>maximum</t>
-  </si>
-  <si>
-    <t>maximum_score_n</t>
-  </si>
-  <si>
-    <t>maximum_score_percent</t>
-  </si>
-  <si>
-    <t>Four-item feedback-experience composite</t>
-  </si>
-  <si>
-    <t>Three-item composite excluding specificity</t>
-  </si>
-  <si>
-    <t>Measurement Decision</t>
-  </si>
-  <si>
-    <t>feature</t>
-  </si>
-  <si>
-    <t>Primary variable</t>
-  </si>
-  <si>
-    <t>feedback_experience</t>
-  </si>
-  <si>
-    <t>Primary variable type</t>
-  </si>
-  <si>
-    <t>Unit-weighted four-item mean/index</t>
-  </si>
-  <si>
-    <t>Primary number of items</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Primary raw alpha</t>
-  </si>
-  <si>
-    <t>0.781</t>
-  </si>
-  <si>
-    <t>Primary standardized alpha</t>
-  </si>
-  <si>
-    <t>0.800</t>
-  </si>
-  <si>
-    <t>Primary ordinal alpha</t>
-  </si>
-  <si>
-    <t>Four-item CFA admissible</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Primary composite mean</t>
-  </si>
-  <si>
-    <t>4.800</t>
-  </si>
-  <si>
-    <t>Primary composite SD</t>
-  </si>
-  <si>
-    <t>Primary maximum-score percentage</t>
-  </si>
-  <si>
-    <t>Sensitivity variable</t>
-  </si>
-  <si>
-    <t>feedback_experience_3item</t>
-  </si>
-  <si>
-    <t>Sensitivity number of items</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sensitivity raw alpha</t>
-  </si>
-  <si>
-    <t>0.631</t>
-  </si>
-  <si>
-    <t>Sensitivity observed omega</t>
-  </si>
-  <si>
-    <t>0.655</t>
-  </si>
-  <si>
-    <t>Correlation between primary and sensitivity scores</t>
-  </si>
-  <si>
-    <t>Phase 4B: AI Comfort</t>
-  </si>
-  <si>
-    <t>Headline Summary</t>
-  </si>
-  <si>
-    <t>finding</t>
-  </si>
-  <si>
-    <t>evidence</t>
-  </si>
-  <si>
-    <t>Final Model Fit</t>
-  </si>
-  <si>
-    <t>selected_model</t>
-  </si>
-  <si>
-    <t>analytic_n</t>
-  </si>
-  <si>
-    <t>number_of_parameters</t>
-  </si>
-  <si>
-    <t>log_likelihood</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>maximum_absolute_gradient</t>
-  </si>
-  <si>
-    <t>hessian_condition_number</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
-    <t>Final linear awareness-scale model</t>
-  </si>
-  <si>
-    <t>logit</t>
-  </si>
-  <si>
-    <t>Verified Model Effects</t>
-  </si>
-  <si>
-    <t>effect</t>
-  </si>
-  <si>
-    <t>effect_type</t>
-  </si>
-  <si>
-    <t>standard_error</t>
-  </si>
-  <si>
-    <t>z_value</t>
-  </si>
-  <si>
-    <t>p_value</t>
-  </si>
-  <si>
-    <t>p_value_display</t>
-  </si>
-  <si>
-    <t>confidence_low</t>
-  </si>
-  <si>
-    <t>confidence_high</t>
-  </si>
-  <si>
-    <t>Extensive prior AI experience versus no experience</t>
-  </si>
-  <si>
-    <t>Location effect</t>
-  </si>
-  <si>
-    <t>= 0.015</t>
-  </si>
-  <si>
-    <t>AI awareness: location effect</t>
-  </si>
-  <si>
-    <t>&lt; .001</t>
-  </si>
-  <si>
-    <t>Feedback experience: 0.5-point increase</t>
-  </si>
-  <si>
-    <t>= 0.008</t>
-  </si>
-  <si>
-    <t>AI awareness: log-scale effect</t>
-  </si>
-  <si>
-    <t>Scale effect</t>
-  </si>
-  <si>
-    <t>= 0.031</t>
-  </si>
-  <si>
-    <t>Adjusted Probabilities by AI Awareness</t>
-  </si>
-  <si>
-    <t>ai_awareness_score</t>
-  </si>
-  <si>
-    <t>ai_awareness</t>
-  </si>
-  <si>
-    <t>predicted_probability</t>
-  </si>
-  <si>
-    <t>Not aware at all</t>
-  </si>
-  <si>
-    <t>Somewhat aware</t>
-  </si>
-  <si>
-    <t>Fully aware</t>
-  </si>
-  <si>
-    <t>Adjusted Probabilities by Feedback Experience and AI Awareness</t>
-  </si>
-  <si>
-    <t>feedback_experience_half_point</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>Final Analysis Decision</t>
-  </si>
-  <si>
-    <t>Final outcome</t>
-  </si>
-  <si>
-    <t>ai_comfort</t>
-  </si>
-  <si>
-    <t>Final model</t>
-  </si>
-  <si>
-    <t>Cumulative-link location-scale model</t>
-  </si>
-  <si>
-    <t>Location predictors</t>
-  </si>
-  <si>
-    <t>Prior AI experience; AI awareness score; feedback-experience composite</t>
-  </si>
-  <si>
-    <t>Scale predictor</t>
-  </si>
-  <si>
-    <t>AI awareness score</t>
-  </si>
-  <si>
-    <t>Link function</t>
-  </si>
-  <si>
-    <t>Logit</t>
-  </si>
-  <si>
-    <t>Threshold structure</t>
-  </si>
-  <si>
-    <t>Flexible</t>
-  </si>
-  <si>
-    <t>Final model AIC</t>
-  </si>
-  <si>
-    <t>406.33</t>
-  </si>
-  <si>
-    <t>Final model BIC</t>
-  </si>
-  <si>
-    <t>437.69</t>
-  </si>
-  <si>
-    <t>Final model log likelihood</t>
-  </si>
-  <si>
-    <t>-193.16</t>
-  </si>
-  <si>
-    <t>Awareness-scale versus benchmark LRT p-value</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>Factor-coded versus linear scale LRT p-value</t>
-  </si>
-  <si>
-    <t>0.947</t>
-  </si>
-  <si>
-    <t>Primary effect-size presentation</t>
-  </si>
-  <si>
-    <t>Adjusted predicted probabilities with 95% confidence intervals</t>
-  </si>
-  <si>
-    <t>Benchmark model role</t>
-  </si>
-  <si>
-    <t>Sensitivity/benchmark proportional-odds odds ratios</t>
-  </si>
-  <si>
-    <t>Displayed feedback-composite range</t>
-  </si>
-  <si>
-    <t>4.00 to 5.00</t>
-  </si>
-  <si>
-    <t>Reason for restricted plotted range</t>
-  </si>
-  <si>
-    <t>97.1% of respondents scored within the displayed range; 71.2% scored at the maximum of 5.00.</t>
-  </si>
-  <si>
-    <t>Phase 4C: Perceived AI Usefulness</t>
-  </si>
-  <si>
-    <t>Outcome Distribution</t>
-  </si>
-  <si>
-    <t>ai_usefulness</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>percent</t>
-  </si>
-  <si>
-    <t>Strongly disagree</t>
-  </si>
-  <si>
-    <t>Somewhat disagree</t>
-  </si>
-  <si>
-    <t>Neither agree nor disagree</t>
-  </si>
-  <si>
-    <t>Somewhat agree</t>
-  </si>
-  <si>
-    <t>Strongly agree</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>convergence_code</t>
-  </si>
-  <si>
-    <t>convergence_message</t>
-  </si>
-  <si>
-    <t>Comfort-added AI-comfort scale model</t>
-  </si>
-  <si>
-    <t>Absolute and relative convergence criteria were met</t>
-  </si>
-  <si>
-    <t>Verified AI-Comfort Effects</t>
-  </si>
-  <si>
-    <t>AI comfort: location effect</t>
-  </si>
-  <si>
-    <t>AI comfort: log-scale effect</t>
-  </si>
-  <si>
-    <t>= 0.005</t>
-  </si>
-  <si>
-    <t>Adjusted Agreement Probabilities by AI Comfort</t>
-  </si>
-  <si>
-    <t>ai_comfort_score</t>
-  </si>
-  <si>
-    <t>confidence_low_raw</t>
-  </si>
-  <si>
-    <t>confidence_high_raw</t>
-  </si>
-  <si>
-    <t>label_y</t>
-  </si>
-  <si>
-    <t>percent_label</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
-    <t>Proportional-Odds Versus Location-Scale Comparison</t>
-  </si>
-  <si>
-    <t>no.par</t>
-  </si>
-  <si>
-    <t>logLik</t>
-  </si>
-  <si>
-    <t>LR.stat</t>
-  </si>
-  <si>
-    <t>Pr(&gt;Chisq)</t>
-  </si>
-  <si>
-    <t>Feedback-Experience Addition Comparison</t>
-  </si>
-  <si>
-    <t>Phase 4D: Preferred Feedback Model</t>
-  </si>
-  <si>
-    <t>Preferred-Model Distribution</t>
-  </si>
-  <si>
-    <t>preferred_model</t>
-  </si>
-  <si>
-    <t>Human-led grading; AI support</t>
-  </si>
-  <si>
-    <t>AI initial feedback; universal human review</t>
-  </si>
-  <si>
-    <t>AI-led feedback; disputed-only human review</t>
-  </si>
-  <si>
-    <t>No preference</t>
-  </si>
-  <si>
-    <t>Human-Review Summary</t>
-  </si>
-  <si>
-    <t>denominator</t>
-  </si>
-  <si>
-    <t>Valid preferred-model responses</t>
-  </si>
-  <si>
-    <t>Expressed a directional model preference</t>
-  </si>
-  <si>
-    <t>Preferred universal human review</t>
-  </si>
-  <si>
-    <t>Preferred disputed-only human review</t>
-  </si>
-  <si>
-    <t>Preferred human-led grading with AI support</t>
-  </si>
-  <si>
-    <t>Preferred AI initial feedback with universal human review</t>
-  </si>
-  <si>
-    <t>Universal review among directional preferences</t>
-  </si>
-  <si>
-    <t>Human-led grading among universal-review preferences</t>
-  </si>
-  <si>
-    <t>Final Model Selection</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>feedback_addition_likelihood_ratio</t>
-  </si>
-  <si>
-    <t>feedback_addition_df</t>
-  </si>
-  <si>
-    <t>feedback_addition_p_value</t>
-  </si>
-  <si>
-    <t>Usefulness-and-feedback multinomial model</t>
-  </si>
-  <si>
-    <t>preferred_model ~ ai_usefulness_score + feedback_experience_half_point</t>
-  </si>
-  <si>
-    <t>Report-Ready Multinomial Coefficients</t>
-  </si>
-  <si>
-    <t>outcome_category</t>
-  </si>
-  <si>
-    <t>reference_category</t>
-  </si>
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>relative_risk_ratio</t>
-  </si>
-  <si>
-    <t>ai_usefulness_score</t>
-  </si>
-  <si>
-    <t>Reduced-Model Likelihood-Ratio Comparisons</t>
-  </si>
-  <si>
-    <t>comparison</t>
-  </si>
-  <si>
-    <t>smaller_model_n</t>
-  </si>
-  <si>
-    <t>larger_model_n</t>
-  </si>
-  <si>
-    <t>smaller_model_log_likelihood</t>
-  </si>
-  <si>
-    <t>larger_model_log_likelihood</t>
-  </si>
-  <si>
-    <t>likelihood_ratio_chisquare</t>
-  </si>
-  <si>
-    <t>Usefulness only versus usefulness plus feedback</t>
-  </si>
-  <si>
-    <t>Feedback only versus feedback plus usefulness</t>
-  </si>
-  <si>
-    <t>Grouped Adjusted Probabilities</t>
-  </si>
-  <si>
-    <t>observed_n</t>
-  </si>
-  <si>
-    <t>preference_group</t>
-  </si>
-  <si>
-    <t>predicted_percent</t>
-  </si>
-  <si>
-    <t>Human-led grading</t>
-  </si>
-  <si>
-    <t>74.9%</t>
-  </si>
-  <si>
-    <t>AI-forward feedback model</t>
-  </si>
-  <si>
-    <t>6.0%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>67.2%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>21.0%</t>
-  </si>
-  <si>
-    <t>55.9%</t>
-  </si>
-  <si>
-    <t>22.6%</t>
-  </si>
-  <si>
-    <t>21.4%</t>
-  </si>
-  <si>
-    <t>40.3%</t>
-  </si>
-  <si>
-    <t>40.8%</t>
-  </si>
-  <si>
-    <t>18.9%</t>
-  </si>
-  <si>
-    <t>22.2%</t>
-  </si>
-  <si>
-    <t>65.0%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
-  </si>
-  <si>
-    <t>Maximum-Likelihood Versus Bias-Reduced Estimates</t>
-  </si>
-  <si>
-    <t>estimate_maximum_likelihood</t>
-  </si>
-  <si>
-    <t>estimate_mean_bias_reduced</t>
-  </si>
-  <si>
-    <t>relative_risk_ratio_maximum_likelihood</t>
-  </si>
-  <si>
-    <t>relative_risk_ratio_mean_bias_reduced</t>
-  </si>
-  <si>
-    <t>absolute_estimate_difference</t>
-  </si>
-  <si>
-    <t>percent_RRR_difference</t>
-  </si>
-  <si>
-    <t>Report-Ready Figures</t>
-  </si>
-  <si>
-    <t>Phase 4A: Feedback-Experience Reliability Diagnostics</t>
-  </si>
-  <si>
-    <t>Phase 4B: Adjusted AI-Comfort Probability by AI Awareness</t>
-  </si>
-  <si>
-    <t>Phase 4C: Adjusted Perceived-Usefulness Probability by AI Comfort</t>
-  </si>
-  <si>
-    <t>Phase 4D: Adjusted Probabilities of Preferred Feedback Models</t>
-  </si>
-  <si>
-    <t>Analysis Source Manifest</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>exists</t>
-  </si>
-  <si>
-    <t>size_kb</t>
-  </si>
-  <si>
-    <t>Phase 4A analysis objects</t>
-  </si>
-  <si>
-    <t>RDS analysis source</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/phase4A_analysis_objects.rds</t>
-  </si>
-  <si>
-    <t>Phase 4A analysis data</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_analysis_phase4A_with_composites.rds</t>
-  </si>
-  <si>
-    <t>Phase 4B final analysis objects</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_final_analysis_objects.rds</t>
-  </si>
-  <si>
-    <t>Phase 4C final checkpoint</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_final_analysis_checkpoint.rds</t>
-  </si>
-  <si>
-    <t>Phase 4C complete-case data</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/learner_analysis_phase4C_complete_cases.rds</t>
-  </si>
-  <si>
-    <t>Phase 4D final checkpoint</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_final_analysis_checkpoint.rds</t>
-  </si>
-  <si>
-    <t>Phase 4D complete-case data</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/learner_analysis_phase4D_complete_cases.rds</t>
-  </si>
-  <si>
-    <t>PNG figure</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_feedback_reliability_plot.png</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_adjusted_probability_by_awareness.png</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_adjusted_usefulness_probability.png</t>
-  </si>
-  <si>
-    <t>C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_adjusted_preferred_model_probabilities.png</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
+  <si>
+    <t xml:space="preserve">Learner Survey: Integrated Phase 4A-4D Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sequence from feedback experience to AI comfort, perceived usefulness, and preferred feedback model is an interpretive and associational synthesis, not a causal or mediation model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analytic_focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key_result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reporting_caution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback-experience measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four feedback items formed a strongly reliable ordinal index (ordinal alpha = 0.903). The composite mean was 4.80, and 71.2% received the maximum score.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current feedback process provides a strong experiential foundation, but the severe ceiling effect limits differentiation among highly positive experiences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four-item CFA was inadmissible; the scale should be described as a reliable unit-weighted index rather than a confirmed latent factor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greater AI comfort was associated with extensive prior AI experience, greater awareness of AI use, and more favorable feedback experience. Adjusted comfort probability increased from 48.6% among respondents not aware of AI use to 82.2% among fully aware respondents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI readiness corresponds with prior exposure, transparency, and learners' experiences of the feedback process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI awareness affected both the location and scale components of comfort, so adjusted probabilities are more interpretable than one proportional-odds ratio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived AI usefulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8% agreed that AI-generated feedback could be as useful as human feedback. Adjusted agreement increased from 1.1% to 90.4% across the AI-comfort scale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI comfort is the clearest bridge between general readiness and believing that AI-generated feedback is useful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The selected location-scale model had an elevated Hessian condition number, so emphasis should remain on adjusted probabilities and the overall pattern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred feedback model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7% preferred a model involving universal human review. The adjusted probability of an AI-forward model increased from 6.0% to 65.0% across perceived AI-usefulness levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learners distinguish between viewing AI as useful and granting AI unrestricted responsibility for feedback or grading.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The multinomial analysis was associational, and sparse predictor-by-outcome cells warrant caution with individual category-specific estimates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Phase Synthesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidence_stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contributing_phases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main_evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrated_interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inference_boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Feedback foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordinal alpha = 0.903; composite mean = 4.80; maximum-score percentage = 71.2%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondents evaluated the existing feedback process exceptionally positively, creating a favorable but compressed foundation for considering AI-supported feedback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scale findings describe measurement quality and response distribution; they do not establish causal effects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Readiness for AI-supported feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phases 4A and 4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensive prior AI experience, AI awareness, and feedback experience were associated with AI comfort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfort with AI appears connected to familiarity, transparency, and experience rather than functioning only as a fixed personal attitude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Phase 4B associations do not demonstrate that awareness or feedback experience causes comfort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Perceived usefulness of AI feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phases 4B and 4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted agreement that AI feedback could be as useful as human feedback increased from 1.1% to 90.4% across AI-comfort levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfort is more proximally connected to perceived AI usefulness than the general feedback-experience index.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sequence from comfort to usefulness is an analytic synthesis, not a tested mediation model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Preferred implementation model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phases 4C and 4D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7% preferred universal human review, while adjusted AI-forward preference increased from 6.0% to 65.0% across perceived usefulness levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greater perceived usefulness corresponds with more AI-forward preferences, but learners continue to place substantial value on universal human review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The preference results show associations and adjusted probabilities, not causal effects of usefulness on model choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated Headline Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistical_evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytic sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 170 respondents had complete data for the four feedback items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordinal alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four-item index demonstrated strong ordinal reliability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average polychoric correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The feedback items were strongly related at the latent-response level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range of polychoric correlations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524 to 0.901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All item pairs were positively associated, although the strength varied across pairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance represented by first component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dominant first component supported summarizing the items with one overall feedback-experience score.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback-experience composite mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learners reported exceptionally favorable feedback experiences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback-experience composite SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The composite displayed limited variability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpret regression estimates in light of the restricted score variation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum-score respondents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pronounced ceiling effect limits differentiation among respondents with very positive feedback experiences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not treat the composite as finely distinguishing highly satisfied respondents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary-sensitivity composite correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four-item and three-item scores produced nearly identical respondent rankings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measurement decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retain the four-item unit-weighted index; do not interpret the inadmissible CFA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four-item index is retained for substantive coverage, with the three-item version used as a sensitivity measure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not report CFA-based omega or global CFA fit because the four-item CFA was inadmissible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensive prior AI experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location coefficient = 4.81, p = 0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondents with extensive prior AI experience reported greater comfort with AI-supported feedback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location coefficient = 1.35, p &lt; .001; log-scale coefficient = 0.258, p = 0.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greater awareness corresponded with higher comfort, but awareness also changed the dispersion of the latent comfort response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awareness affected both location and scale; use adjusted probabilities for interpretation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location coefficient per 0.5-point increase = 0.669, p = 0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More favorable feedback experiences were associated with greater AI comfort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted comfort probability by awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability of somewhat or strongly agreeing with AI comfort: 48.6% among respondents not aware of AI use, 71.8% among somewhat aware respondents, and 82.2% among fully aware respondents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The adjusted probabilities show a substantial increase in comfort across awareness levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative-link location-scale model; AIC = 406.33.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because awareness affected both location and scale, adjusted probabilities are preferable to a single proportional-odds ratio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hessian condition number was elevated, so large individual coefficients should be interpreted cautiously.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed perceived usefulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117 of 170 respondents (68.8%) somewhat or strongly agreed that AI-generated feedback could be as useful as human feedback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A majority of respondents viewed AI-generated feedback as potentially comparable in usefulness to human feedback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location coefficient = 3.68, p &lt; .001; log-scale coefficient = 0.272, p = 0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI comfort was strongly associated with perceived AI usefulness and also affected latent-response dispersion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfort affected both location and scale; adjusted probabilities are the primary effect-size presentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted usefulness probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted agreement probability increased from 1.1% at the lowest comfort level to 90.4% at the highest comfort level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfort clearly distinguished respondents with low versus high adjusted probabilities of viewing AI feedback as useful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location-scale model improvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likelihood-ratio test p = 0.004; selected-model AIC = 359.23.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The location-scale model fit better than the proportional-odds benchmark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The selected model had an elevated Hessian condition number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback-experience contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding feedback experience after AI comfort: likelihood-ratio test p = 0.917.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback experience did not improve the usefulness model after AI comfort was included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest preferred-model category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-led grading with AI support: 66 of 169 respondents (39.1%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The most common single preference retained instructor control and used AI only as a support tool.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111 of 169 respondents (65.7%) preferred universal human review. Among respondents with a directional preference, the percentage was 79.9%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learners generally accepted AI assistance while retaining a strong preference for universal human accountability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding perceived usefulness to a feedback-only model: likelihood-ratio test p &lt; .001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived AI usefulness substantially distinguished preferred feedback models.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpret omnibus likelihood-ratio tests alongside category-specific coefficients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding feedback experience to a usefulness-only model: likelihood-ratio test p = 0.010.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback experience improved overall model fit even though its individual category-specific Wald coefficients were not statistically significant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted AI-forward preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted probability of an AI-forward feedback model increased from 6.0% among respondents who strongly disagreed that AI feedback was as useful as human feedback to 65.0% among those who strongly agreed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More favorable perceptions of AI usefulness corresponded with substantially more AI-forward implementation preferences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The results are associational, and some predictor-by-outcome cells were sparse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4A: Feedback-Experience Scale Diagnostics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headline Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polychoric Correlation Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubric_clear_aligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_specific_relevant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_helped_improve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_timely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordinal Item Diagnostics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordinal_item_rest_correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordinal_alpha_if_deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_score_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_score_percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-item feedback-experience composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three-item composite excluding specificity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measurement Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary variable type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit-weighted four-item mean/index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary number of items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary raw alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary standardized alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary ordinal alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-item CFA admissible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary composite mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary composite SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary maximum-score percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_experience_3item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity number of items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity raw alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity observed omega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlation between primary and sensitivity scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4B: AI Comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headline Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Model Fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analytic_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number_of_parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_absolute_gradient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hessian_condition_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final linear awareness-scale model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified Model Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effect_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_value_display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence_low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence_high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensive prior AI experience versus no experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">= 0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI awareness: location effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; .001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback experience: 0.5-point increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">= 0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI awareness: log-scale effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">= 0.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted Probabilities by AI Awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_awareness_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">predicted_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not aware at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somewhat aware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fully aware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted Probabilities by Feedback Experience and AI Awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_experience_half_point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Analysis Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative-link location-scale model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location predictors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior AI experience; AI awareness score; feedback-experience composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale predictor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI awareness score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final model AIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final model BIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">437.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final model log likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-193.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awareness-scale versus benchmark LRT p-value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor-coded versus linear scale LRT p-value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary effect-size presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted predicted probabilities with 95% confidence intervals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benchmark model role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity/benchmark proportional-odds odds ratios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Displayed feedback-composite range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00 to 5.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason for restricted plotted range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1% of respondents scored within the displayed range; 71.2% scored at the maximum of 5.00.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4C: Perceived AI Usefulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_usefulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongly disagree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somewhat disagree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neither agree nor disagree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somewhat agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongly agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">convergence_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">convergence_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfort-added AI-comfort scale model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute and relative convergence criteria were met</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified AI-Comfort Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI comfort: location effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI comfort: log-scale effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">= 0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted Agreement Probabilities by AI Comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_comfort_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence_low_raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence_high_raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportional-Odds Versus Location-Scale Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no.par</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR.stat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr(&gt;Chisq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback-Experience Addition Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4D: Preferred Feedback Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred-Model Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-led grading; AI support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI initial feedback; universal human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-led feedback; disputed-only human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-Review Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">denominator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid preferred-model responses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expressed a directional model preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred universal human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred disputed-only human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred human-led grading with AI support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred AI initial feedback with universal human review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal review among directional preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-led grading among universal-review preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Model Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_addition_likelihood_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_addition_df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feedback_addition_p_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usefulness-and-feedback multinomial model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preferred_model ~ ai_usefulness_score + feedback_experience_half_point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report-Ready Multinomial Coefficients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference_category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative_risk_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_usefulness_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced-Model Likelihood-Ratio Comparisons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smaller_model_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">larger_model_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smaller_model_log_likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">larger_model_log_likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">likelihood_ratio_chisquare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usefulness only versus usefulness plus feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback only versus feedback plus usefulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grouped Adjusted Probabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observed_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preference_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">predicted_percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-led grading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-forward feedback model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum-Likelihood Versus Bias-Reduced Estimates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate_maximum_likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate_mean_bias_reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative_risk_ratio_maximum_likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relative_risk_ratio_mean_bias_reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute_estimate_difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_RRR_difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report-Ready Figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4A: Feedback-Experience Reliability Diagnostics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4B: Adjusted AI-Comfort Probability by AI Awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4C: Adjusted Perceived-Usefulness Probability by AI Comfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4D: Adjusted Probabilities of Preferred Feedback Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysis Source Manifest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">size_kb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4A analysis objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDS analysis source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/phase4A_analysis_objects.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4A analysis data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_analysis_phase4A_with_composites.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4B final analysis objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_final_analysis_objects.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4C final checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_final_analysis_checkpoint.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4C complete-case data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/learner_analysis_phase4C_complete_cases.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4D final checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_final_analysis_checkpoint.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4D complete-case data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/learner_analysis_phase4D_complete_cases.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNG figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_scale_diagnostics/learner_feedback_reliability_plot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_comfort_ordinal/final/phase4B_adjusted_probability_by_awareness.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_ai_usefulness_ordinal/phase4C_adjusted_usefulness_probability.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/wangpinyi/Desktop/Lastinger/assessment-feedback-analysis/output/learner_preferred_model_multinomial/phase4D_adjusted_preferred_model_probabilities.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1245,22 +1238,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <i/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="11"/>
@@ -1285,13 +1278,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1319,155 +1308,126 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
+      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
+      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">3</xdr:row>
+      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9601200" cy="5852160"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
+    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Picture 1"/>
+        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
+      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        </a:blip>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
+      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
+      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">31</xdr:row>
+      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9601200" cy="5852160"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
+    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Picture 2"/>
+        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
+      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        </a:blip>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
+      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
+      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">59</xdr:row>
+      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9601200" cy="5852160"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
+    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="3" name="Picture 3"/>
+        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
+      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        </a:blip>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
+      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
+      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">87</xdr:row>
+      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9601200" cy="5852160"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="9601200" cy="5852160"/>
+    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="4" name="Picture 4"/>
+        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
+      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        </a:blip>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
@@ -1754,32 +1714,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="52.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1796,7 +1757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1813,7 +1774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -1830,7 +1791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1847,7 +1808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -1864,12 +1825,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
@@ -1886,7 +1847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -1903,7 +1864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
@@ -1920,7 +1881,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
@@ -1937,7 +1898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
@@ -1956,29 +1917,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="6" width="50.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="38.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="50.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="50.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="46.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2001,7 +1963,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +1982,7 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2001,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2058,7 +2020,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2077,7 +2039,7 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2096,7 +2058,7 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2115,7 +2077,7 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2136,7 +2098,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2157,7 +2119,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2176,7 +2138,7 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2159,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -2216,7 +2178,7 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2199,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
@@ -2256,7 +2218,7 @@
       </c>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -2275,7 +2237,7 @@
       </c>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -2296,7 +2258,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -2315,7 +2277,7 @@
       </c>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="48" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -2336,7 +2298,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -2355,7 +2317,7 @@
       </c>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
@@ -2376,7 +2338,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
@@ -2395,7 +2357,7 @@
       </c>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
@@ -2414,7 +2376,7 @@
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -2433,7 +2395,7 @@
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -2454,7 +2416,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -2475,7 +2437,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>23</v>
       </c>
@@ -2498,32 +2460,38 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="10" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="34.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="34.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>141</v>
       </c>
@@ -2537,7 +2505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>58</v>
       </c>
@@ -2549,7 +2517,7 @@
       </c>
       <c r="D5" s="5"/>
     </row>
-    <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>61</v>
       </c>
@@ -2561,7 +2529,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>64</v>
       </c>
@@ -2573,7 +2541,7 @@
       </c>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>67</v>
       </c>
@@ -2585,7 +2553,7 @@
       </c>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
@@ -2597,7 +2565,7 @@
       </c>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>73</v>
       </c>
@@ -2609,7 +2577,7 @@
       </c>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -2623,7 +2591,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>80</v>
       </c>
@@ -2637,7 +2605,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>84</v>
       </c>
@@ -2649,7 +2617,7 @@
       </c>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>87</v>
       </c>
@@ -2663,12 +2631,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="4" t="s">
         <v>143</v>
       </c>
@@ -2685,80 +2653,80 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="5">
-        <v>0.79751847331386305</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="5" t="n">
+        <v>0.797518473313863</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>0.699283935466114</v>
       </c>
-      <c r="E19" s="5">
-        <v>0.52358960364957796</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="5" t="n">
+        <v>0.523589603649578</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="5">
-        <v>0.79751847331386305</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="5" t="n">
+        <v>0.797518473313863</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="5">
-        <v>0.90061272937644798</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.68608809456450903</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="5" t="n">
+        <v>0.900612729376448</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.686088094564509</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="5" t="n">
         <v>0.699283935466114</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.90061272937644798</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="5" t="n">
+        <v>0.900612729376448</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="5">
-        <v>0.59680666568888097</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="5" t="n">
+        <v>0.596806665688881</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B22" s="5">
-        <v>0.52358960364957796</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0.68608809456450903</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.59680666568888097</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="B22" s="5" t="n">
+        <v>0.523589603649578</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.686088094564509</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.596806665688881</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="4" t="s">
         <v>143</v>
       </c>
@@ -2769,56 +2737,56 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="5">
-        <v>0.74437172216787195</v>
-      </c>
-      <c r="C27" s="5">
-        <v>0.88916915295152399</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="n">
+        <v>0.744371722167872</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.889169152951524</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="5">
-        <v>0.92530109583880904</v>
-      </c>
-      <c r="C28" s="5">
-        <v>0.82222387061754498</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="n">
+        <v>0.925301095838809</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.822223870617545</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="5">
-        <v>0.82942358674226602</v>
-      </c>
-      <c r="C29" s="5">
+      <c r="B29" s="5" t="n">
+        <v>0.829423586742266</v>
+      </c>
+      <c r="C29" s="5" t="n">
         <v>0.858461890935584</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="5">
-        <v>0.64703962100244805</v>
-      </c>
-      <c r="C30" s="5">
-        <v>0.92269429346335796</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="n">
+        <v>0.647039621002448</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.922694293463358</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="4" t="s">
         <v>152</v>
       </c>
@@ -2844,64 +2812,64 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="D35" s="5">
-        <v>0.43650033720341902</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35" s="5" t="n">
+        <v>0.436500337203419</v>
+      </c>
+      <c r="E35" s="5" t="n">
         <v>2.25</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="H35" s="5">
-        <v>71.176470588235304</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="5" t="n">
+        <v>71.1764705882353</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="C36" s="5">
-        <v>4.7901960784313697</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="5" t="n">
+        <v>4.79019607843137</v>
+      </c>
+      <c r="D36" s="5" t="n">
         <v>0.433365907724587</v>
       </c>
-      <c r="E36" s="5">
-        <v>2.3333333333333299</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="E36" s="5" t="n">
+        <v>2.33333333333333</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="H36" s="5">
-        <v>71.176470588235304</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="5" t="n">
+        <v>71.1764705882353</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="4" t="s">
         <v>163</v>
       </c>
@@ -2909,7 +2877,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="s">
         <v>164</v>
       </c>
@@ -2917,7 +2885,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="s">
         <v>166</v>
       </c>
@@ -2925,7 +2893,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="s">
         <v>168</v>
       </c>
@@ -2933,7 +2901,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="s">
         <v>170</v>
       </c>
@@ -2941,7 +2909,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="s">
         <v>172</v>
       </c>
@@ -2949,7 +2917,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="s">
         <v>174</v>
       </c>
@@ -2957,7 +2925,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2965,7 +2933,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2973,7 +2941,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2981,7 +2949,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="s">
         <v>180</v>
       </c>
@@ -2989,7 +2957,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="s">
         <v>181</v>
       </c>
@@ -2997,7 +2965,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="s">
         <v>183</v>
       </c>
@@ -3005,7 +2973,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="s">
         <v>185</v>
       </c>
@@ -3013,7 +2981,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="s">
         <v>187</v>
       </c>
@@ -3021,7 +2989,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="s">
         <v>189</v>
       </c>
@@ -3031,32 +2999,39 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="46.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="11" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="46.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="34.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -3067,7 +3042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>91</v>
       </c>
@@ -3078,7 +3053,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -3089,7 +3064,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>98</v>
       </c>
@@ -3100,7 +3075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>101</v>
       </c>
@@ -3111,7 +3086,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>104</v>
       </c>
@@ -3122,12 +3097,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="4" t="s">
         <v>195</v>
       </c>
@@ -3156,41 +3131,41 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="5">
-        <v>-193.16482364425499</v>
-      </c>
-      <c r="E14" s="5">
-        <v>406.32964728850999</v>
-      </c>
-      <c r="F14" s="5">
-        <v>437.68763165901203</v>
-      </c>
-      <c r="G14" s="5">
-        <v>3.2702876295864802E-8</v>
-      </c>
-      <c r="H14" s="5">
+      <c r="D14" s="5" t="n">
+        <v>-193.164823644255</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>406.32964728851</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>437.687631659012</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0000000327028762958648</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>1301.31627807825</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="4" t="s">
         <v>207</v>
       </c>
@@ -3219,128 +3194,128 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>215</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="5">
-        <v>4.8072506699175701</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="5" t="n">
+        <v>4.80725066991757</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>1.97850804623326</v>
       </c>
-      <c r="E19" s="5">
-        <v>2.4297352133946299</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1.5109857088528701E-2</v>
+      <c r="E19" s="5" t="n">
+        <v>2.42973521339463</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.0151098570885287</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="H19" s="5">
-        <v>0.92944615617767201</v>
-      </c>
-      <c r="I19" s="5">
-        <v>8.6850551836574699</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="5" t="n">
+        <v>0.929446156177672</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>8.68505518365747</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>218</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="5">
-        <v>1.3511782186394901</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.36004752334816698</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="C20" s="5" t="n">
+        <v>1.35117821863949</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.360047523348167</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>3.75277742803106</v>
       </c>
-      <c r="F20" s="5">
-        <v>1.748861191692E-4</v>
+      <c r="F20" s="5" t="n">
+        <v>0.0001748861191692</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H20" s="5">
-        <v>0.64549804015423695</v>
-      </c>
-      <c r="I20" s="5">
-        <v>2.0568583971247398</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="5" t="n">
+        <v>0.645498040154237</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2.05685839712474</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>220</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.66936004761821699</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.25433623691395002</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="C21" s="5" t="n">
+        <v>0.669360047618217</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.25433623691395</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>2.63179189776517</v>
       </c>
-      <c r="F21" s="5">
-        <v>8.4935870229608402E-3</v>
+      <c r="F21" s="5" t="n">
+        <v>0.00849358702296084</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="5">
-        <v>0.17087018330342699</v>
-      </c>
-      <c r="I21" s="5">
-        <v>1.1678499119330099</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H21" s="5" t="n">
+        <v>0.170870183303427</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1.16784991193301</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>222</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="5">
-        <v>0.25817098671796201</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="5" t="n">
+        <v>0.258170986717962</v>
+      </c>
+      <c r="D22" s="5" t="n">
         <v>0.119985187009894</v>
       </c>
-      <c r="E22" s="5">
-        <v>2.1516904974001001</v>
-      </c>
-      <c r="F22" s="5">
-        <v>3.1421739071155398E-2</v>
+      <c r="E22" s="5" t="n">
+        <v>2.1516904974001</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.0314217390711554</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="H22" s="5">
-        <v>2.30043415002672E-2</v>
-      </c>
-      <c r="I22" s="5">
+      <c r="H22" s="5" t="n">
+        <v>0.0230043415002672</v>
+      </c>
+      <c r="I22" s="5" t="n">
         <v>0.493337631935657</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="4" t="s">
         <v>226</v>
       </c>
@@ -3360,72 +3335,72 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C27" s="5">
-        <v>0.48643571979869898</v>
-      </c>
-      <c r="D27" s="5">
-        <v>7.5542580668872802E-2</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="C27" s="5" t="n">
+        <v>0.486435719798699</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.0755425806688728</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>0.338374982388497</v>
       </c>
-      <c r="F27" s="5">
-        <v>0.63449645720890202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="F27" s="5" t="n">
+        <v>0.634496457208902</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="5">
-        <v>0.71754824601539002</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3.9724378260617602E-2</v>
-      </c>
-      <c r="E28" s="5">
-        <v>0.63968989531633402</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0.79540659671444702</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+      <c r="C28" s="5" t="n">
+        <v>0.71754824601539</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.0397243782606176</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.639689895316334</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.795406596714447</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="5">
-        <v>0.82185610966455103</v>
-      </c>
-      <c r="D29" s="5">
-        <v>3.3584291281325201E-2</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0.75603210830685097</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0.88768011102225097</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C29" s="5" t="n">
+        <v>0.821856109664551</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.0335842912813252</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.756032108306851</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.887680111022251</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="4" t="s">
         <v>233</v>
       </c>
@@ -3454,447 +3429,447 @@
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="5">
-        <v>0.28730994304539598</v>
-      </c>
-      <c r="D34" s="5">
-        <v>8.2049349124095006E-2</v>
+      <c r="C34" s="5" t="n">
+        <v>0.287309943045396</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.082049349124095</v>
       </c>
       <c r="E34" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F34" s="5">
-        <v>0.12649617380721601</v>
-      </c>
-      <c r="G34" s="5">
+      <c r="F34" s="5" t="n">
+        <v>0.126496173807216</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>0.448123712283575</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="B35" s="5">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="B35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="5">
-        <v>0.34235309229204203</v>
-      </c>
-      <c r="D35" s="5">
-        <v>7.9802758198717197E-2</v>
+      <c r="C35" s="5" t="n">
+        <v>0.342353092292042</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0.0798027581987172</v>
       </c>
       <c r="E35" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5" t="n">
         <v>0.185942560355598</v>
       </c>
-      <c r="G35" s="5">
-        <v>0.49876362422848602</v>
+      <c r="G35" s="5" t="n">
+        <v>0.498763624228486</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="5" t="n">
         <v>4.25</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="5">
-        <v>0.40461421545854198</v>
-      </c>
-      <c r="D36" s="5">
-        <v>7.6384026227907506E-2</v>
+      <c r="C36" s="5" t="n">
+        <v>0.404614215458542</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.0763840262279075</v>
       </c>
       <c r="E36" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F36" s="5">
-        <v>0.25490427505768098</v>
-      </c>
-      <c r="G36" s="5">
-        <v>0.55432415585940398</v>
+      <c r="F36" s="5" t="n">
+        <v>0.254904275057681</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.554324155859404</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>-9.9999999999999603E-2</v>
-      </c>
-      <c r="B37" s="5">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>-0.0999999999999996</v>
+      </c>
+      <c r="B37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="5" t="n">
         <v>0.472417077245325</v>
       </c>
-      <c r="D37" s="5">
-        <v>7.5199196320309594E-2</v>
+      <c r="D37" s="5" t="n">
+        <v>0.0751991963203096</v>
       </c>
       <c r="E37" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F37" s="5">
-        <v>0.32502936079116201</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0.61980479369948904</v>
+      <c r="F37" s="5" t="n">
+        <v>0.325029360791162</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.619804793699489</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="5" t="n">
         <v>4.75</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="5" t="n">
         <v>0.54328007762816</v>
       </c>
-      <c r="D38" s="5">
-        <v>7.9227419334642404E-2</v>
+      <c r="D38" s="5" t="n">
+        <v>0.0792274193346424</v>
       </c>
       <c r="E38" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="5" t="n">
         <v>0.387997189144208</v>
       </c>
-      <c r="G38" s="5">
-        <v>0.69856296611211099</v>
+      <c r="G38" s="5" t="n">
+        <v>0.698562966112111</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="5">
-        <v>0.54412154607822205</v>
-      </c>
-      <c r="D39" s="5">
-        <v>7.5024492594474607E-2</v>
+      <c r="C39" s="5" t="n">
+        <v>0.544121546078222</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0.0750244925944746</v>
       </c>
       <c r="E39" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F39" s="5">
-        <v>0.39707624263466001</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0.69116684952178398</v>
+      <c r="F39" s="5" t="n">
+        <v>0.39707624263466</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.691166849521784</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="B40" s="5">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="B40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="5">
-        <v>0.60087741913360304</v>
-      </c>
-      <c r="D40" s="5">
-        <v>5.9425357182765599E-2</v>
+      <c r="C40" s="5" t="n">
+        <v>0.600877419133603</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0.0594253571827656</v>
       </c>
       <c r="E40" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F40" s="5">
-        <v>0.48440585928695401</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0.71734897898025296</v>
+      <c r="F40" s="5" t="n">
+        <v>0.484405859286954</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.717348978980253</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="5" t="n">
         <v>4.25</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="5">
-        <v>0.65587113683320097</v>
-      </c>
-      <c r="D41" s="5">
-        <v>4.6831987396521703E-2</v>
+      <c r="C41" s="5" t="n">
+        <v>0.655871136833201</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.0468319873965217</v>
       </c>
       <c r="E41" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F41" s="5">
-        <v>0.56408212821158499</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0.74766014545481796</v>
+      <c r="F41" s="5" t="n">
+        <v>0.564082128211585</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.747660145454818</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>-9.9999999999999603E-2</v>
-      </c>
-      <c r="B42" s="5">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>-0.0999999999999996</v>
+      </c>
+      <c r="B42" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="5">
-        <v>0.70767574395690602</v>
-      </c>
-      <c r="D42" s="5">
-        <v>4.02166036320298E-2</v>
+      <c r="C42" s="5" t="n">
+        <v>0.707675743956906</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0.0402166036320298</v>
       </c>
       <c r="E42" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F42" s="5">
-        <v>0.62885264925760498</v>
-      </c>
-      <c r="G42" s="5">
-        <v>0.78649883865620696</v>
+      <c r="F42" s="5" t="n">
+        <v>0.628852649257605</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.786498838656207</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="5" t="n">
         <v>4.75</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="5">
-        <v>0.75516298084495403</v>
-      </c>
-      <c r="D43" s="5">
-        <v>3.9989601134209102E-2</v>
+      <c r="C43" s="5" t="n">
+        <v>0.755162980844954</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.0399896011342091</v>
       </c>
       <c r="E43" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F43" s="5">
-        <v>0.67678480286578302</v>
-      </c>
-      <c r="G43" s="5">
-        <v>0.83354115882412605</v>
+      <c r="F43" s="5" t="n">
+        <v>0.676784802865783</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.833541158824126</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="5">
-        <v>0.71421620254240403</v>
-      </c>
-      <c r="D44" s="5">
-        <v>5.8159738685878197E-2</v>
+      <c r="C44" s="5" t="n">
+        <v>0.714216202542404</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.0581597386858782</v>
       </c>
       <c r="E44" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F44" s="5">
-        <v>0.60022520936782198</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0.82820719571698598</v>
+      <c r="F44" s="5" t="n">
+        <v>0.600225209367822</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.828207195716986</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="B45" s="5">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="B45" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="5">
-        <v>0.75141232181092699</v>
-      </c>
-      <c r="D45" s="5">
-        <v>4.6606836355161697E-2</v>
+      <c r="C45" s="5" t="n">
+        <v>0.751412321810927</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.0466068363551617</v>
       </c>
       <c r="E45" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F45" s="5">
-        <v>0.66006460112145804</v>
-      </c>
-      <c r="G45" s="5">
-        <v>0.84276004250039604</v>
+      <c r="F45" s="5" t="n">
+        <v>0.660064601121458</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.842760042500396</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="5" t="n">
         <v>4.25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="5">
-        <v>0.78544036541420603</v>
-      </c>
-      <c r="D46" s="5">
-        <v>3.8524571566717902E-2</v>
+      <c r="C46" s="5" t="n">
+        <v>0.785440365414206</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0.0385245715667179</v>
       </c>
       <c r="E46" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="5" t="n">
         <v>0.709933592623603</v>
       </c>
-      <c r="G46" s="5">
-        <v>0.86094713820480895</v>
+      <c r="G46" s="5" t="n">
+        <v>0.860947138204809</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>-9.9999999999999603E-2</v>
-      </c>
-      <c r="B47" s="5">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>-0.0999999999999996</v>
+      </c>
+      <c r="B47" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="5">
-        <v>0.81612544831427802</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3.40878822530611E-2</v>
+      <c r="C47" s="5" t="n">
+        <v>0.816125448314278</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.0340878822530611</v>
       </c>
       <c r="E47" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F47" s="5">
-        <v>0.74931442678903604</v>
-      </c>
-      <c r="G47" s="5">
-        <v>0.88293646983951901</v>
+      <c r="F47" s="5" t="n">
+        <v>0.749314426789036</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.882936469839519</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="5" t="n">
         <v>4.75</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="5">
-        <v>0.84343403499943803</v>
-      </c>
-      <c r="D48" s="5">
-        <v>3.25105317671684E-2</v>
+      <c r="C48" s="5" t="n">
+        <v>0.843434034999438</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.0325105317671684</v>
       </c>
       <c r="E48" s="5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F48" s="5">
-        <v>0.77971456361754299</v>
-      </c>
-      <c r="G48" s="5">
-        <v>0.90715350638133396</v>
+      <c r="F48" s="5" t="n">
+        <v>0.779714563617543</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.907153506381334</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" s="4" t="s">
         <v>163</v>
       </c>
@@ -3902,7 +3877,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="s">
         <v>237</v>
       </c>
@@ -3910,7 +3885,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="s">
         <v>239</v>
       </c>
@@ -3918,7 +3893,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="s">
         <v>241</v>
       </c>
@@ -3926,7 +3901,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="s">
         <v>243</v>
       </c>
@@ -3934,7 +3909,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="s">
         <v>245</v>
       </c>
@@ -3942,7 +3917,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="s">
         <v>247</v>
       </c>
@@ -3950,7 +3925,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="s">
         <v>249</v>
       </c>
@@ -3958,7 +3933,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="s">
         <v>251</v>
       </c>
@@ -3966,7 +3941,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="s">
         <v>253</v>
       </c>
@@ -3974,7 +3949,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="s">
         <v>255</v>
       </c>
@@ -3982,7 +3957,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="s">
         <v>257</v>
       </c>
@@ -3990,7 +3965,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="s">
         <v>259</v>
       </c>
@@ -3998,7 +3973,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="s">
         <v>261</v>
       </c>
@@ -4006,7 +3981,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="s">
         <v>263</v>
       </c>
@@ -4014,7 +3989,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="s">
         <v>265</v>
       </c>
@@ -4024,32 +3999,39 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="44.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="11" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="44.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="34.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -4060,7 +4042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>108</v>
       </c>
@@ -4071,7 +4053,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -4082,7 +4064,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>114</v>
       </c>
@@ -4093,7 +4075,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>117</v>
       </c>
@@ -4104,7 +4086,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>121</v>
       </c>
@@ -4115,12 +4097,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="4" t="s">
         <v>269</v>
       </c>
@@ -4131,67 +4113,67 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="5">
-        <v>4.1176470588235299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="5" t="n">
+        <v>4.11764705882353</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C15" s="5">
-        <v>11.764705882352899</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="5" t="n">
+        <v>11.7647058823529</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C16" s="5">
-        <v>15.294117647058799</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="5" t="n">
+        <v>15.2941176470588</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="C17" s="5">
-        <v>32.352941176470601</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="5" t="n">
+        <v>32.3529411764706</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="C18" s="5">
-        <v>36.470588235294102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C18" s="5" t="n">
+        <v>36.4705882352941</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="4" t="s">
         <v>277</v>
       </c>
@@ -4226,47 +4208,47 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="5" t="n">
         <v>-169.61435196904</v>
       </c>
-      <c r="E23" s="5">
-        <v>359.22870393808103</v>
-      </c>
-      <c r="F23" s="5">
-        <v>390.58668830858301</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="E23" s="5" t="n">
+        <v>359.228703938081</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>390.586688308583</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="I23" s="5">
-        <v>3.2134295224750499E-12</v>
-      </c>
-      <c r="J23" s="5">
+      <c r="I23" s="5" t="n">
+        <v>0.00000000000321342952247505</v>
+      </c>
+      <c r="J23" s="5" t="n">
         <v>38408.2228436937</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" s="4" t="s">
         <v>207</v>
       </c>
@@ -4289,58 +4271,58 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>283</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="5">
-        <v>3.6773642271081801</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1.0456686040229399</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="C28" s="5" t="n">
+        <v>3.67736422710818</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.04566860402294</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>3.51675876368523</v>
       </c>
-      <c r="F28" s="5">
-        <v>4.36850616945304E-4</v>
+      <c r="F28" s="5" t="n">
+        <v>0.000436850616945304</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>284</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="5" t="n">
         <v>0.271512289987278</v>
       </c>
-      <c r="D29" s="5">
-        <v>9.6388973791838806E-2</v>
-      </c>
-      <c r="E29" s="5">
-        <v>2.8168397204189999</v>
-      </c>
-      <c r="F29" s="5">
-        <v>4.8498721855183601E-3</v>
+      <c r="D29" s="5" t="n">
+        <v>0.0963889737918388</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2.816839720419</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.00484987218551836</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="4" t="s">
         <v>287</v>
       </c>
@@ -4372,172 +4354,172 @@
         <v>291</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C34" s="5">
-        <v>1.08715978052725E-2</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2.8084273301759201E-2</v>
-      </c>
-      <c r="E34" s="5">
-        <v>-4.4172566398155297E-2</v>
-      </c>
-      <c r="F34" s="5">
-        <v>6.5915762008700293E-2</v>
-      </c>
-      <c r="G34" s="5">
+      <c r="C34" s="5" t="n">
+        <v>0.0108715978052725</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.0280842733017592</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-0.0441725663981553</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.0659157620087003</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="5">
-        <v>6.5915762008700293E-2</v>
-      </c>
-      <c r="I34" s="5">
+      <c r="H34" s="5" t="n">
+        <v>0.0659157620087003</v>
+      </c>
+      <c r="I34" s="5" t="n">
         <v>0.1059157620087</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C35" s="5">
-        <v>9.6256454800200703E-2</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.99685883663237E-2</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1.79194610892996E-2</v>
-      </c>
-      <c r="F35" s="5">
-        <v>0.17459344851110201</v>
-      </c>
-      <c r="G35" s="5">
-        <v>1.79194610892996E-2</v>
-      </c>
-      <c r="H35" s="5">
-        <v>0.17459344851110201</v>
-      </c>
-      <c r="I35" s="5">
-        <v>0.21459344851110199</v>
+      <c r="C35" s="5" t="n">
+        <v>0.0962564548002007</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0.0399685883663237</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.0179194610892996</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.174593448511102</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0179194610892996</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.174593448511102</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.214593448511102</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C36" s="5">
-        <v>0.41824319094803902</v>
-      </c>
-      <c r="D36" s="5">
-        <v>6.2193151109490301E-2</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0.29634685468838101</v>
-      </c>
-      <c r="F36" s="5">
-        <v>0.54013952720769698</v>
-      </c>
-      <c r="G36" s="5">
-        <v>0.29634685468838101</v>
-      </c>
-      <c r="H36" s="5">
-        <v>0.54013952720769698</v>
-      </c>
-      <c r="I36" s="5">
-        <v>0.58013952720769701</v>
+      <c r="C36" s="5" t="n">
+        <v>0.418243190948039</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.0621931511094903</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.296346854688381</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.540139527207697</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.296346854688381</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.540139527207697</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.580139527207697</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="5">
-        <v>0.78664021300532605</v>
-      </c>
-      <c r="D37" s="5">
-        <v>3.6142135187641401E-2</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0.71580292971317105</v>
-      </c>
-      <c r="F37" s="5">
-        <v>0.85747749629748105</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0.71580292971317105</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0.85747749629748105</v>
-      </c>
-      <c r="I37" s="5">
-        <v>0.89747749629748097</v>
+      <c r="C37" s="5" t="n">
+        <v>0.786640213005326</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.0361421351876414</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.715802929713171</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.857477496297481</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.715802929713171</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.857477496297481</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.897477496297481</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C38" s="5">
-        <v>0.90383967963936096</v>
-      </c>
-      <c r="D38" s="5">
-        <v>2.94415655543733E-2</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="C38" s="5" t="n">
+        <v>0.903839679639361</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0.0294415655543733</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>0.846135271504315</v>
       </c>
-      <c r="F38" s="5">
-        <v>0.96154408777440803</v>
-      </c>
-      <c r="G38" s="5">
+      <c r="F38" s="5" t="n">
+        <v>0.961544087774408</v>
+      </c>
+      <c r="G38" s="5" t="n">
         <v>0.846135271504315</v>
       </c>
-      <c r="H38" s="5">
-        <v>0.96154408777440803</v>
-      </c>
-      <c r="I38" s="5">
+      <c r="H38" s="5" t="n">
+        <v>0.961544087774408</v>
+      </c>
+      <c r="I38" s="5" t="n">
         <v>1.00154408777441</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" s="4" t="s">
         <v>298</v>
       </c>
@@ -4557,46 +4539,46 @@
         <v>301</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B43" s="5">
-        <v>365.33677598408798</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-173.66838799204399</v>
+      <c r="B43" s="5" t="n">
+        <v>365.336775984088</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>-173.668387992044</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B44" s="5">
-        <v>359.22870393808103</v>
-      </c>
-      <c r="C44" s="5">
+      <c r="B44" s="5" t="n">
+        <v>359.228703938081</v>
+      </c>
+      <c r="C44" s="5" t="n">
         <v>-169.61435196904</v>
       </c>
-      <c r="D44" s="5">
-        <v>8.1080720460075195</v>
-      </c>
-      <c r="E44" s="5">
+      <c r="D44" s="5" t="n">
+        <v>8.10807204600752</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="5">
-        <v>4.4068572179397003E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F44" s="5" t="n">
+        <v>0.0044068572179397</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="3" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" s="4" t="s">
         <v>298</v>
       </c>
@@ -4616,68 +4598,76 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B49" s="5">
-        <v>359.22870393808103</v>
-      </c>
-      <c r="C49" s="5">
+      <c r="B49" s="5" t="n">
+        <v>359.228703938081</v>
+      </c>
+      <c r="C49" s="5" t="n">
         <v>-169.61435196904</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
     </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B50" s="5">
-        <v>361.21789400393499</v>
-      </c>
-      <c r="C50" s="5">
+      <c r="B50" s="5" t="n">
+        <v>361.217894003935</v>
+      </c>
+      <c r="C50" s="5" t="n">
         <v>-169.608947001968</v>
       </c>
-      <c r="D50" s="5">
-        <v>1.0809934145072499E-2</v>
-      </c>
-      <c r="E50" s="5">
+      <c r="D50" s="5" t="n">
+        <v>0.0108099341450725</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="5">
-        <v>0.91719249487478305</v>
+      <c r="F50" s="5" t="n">
+        <v>0.917192494874783</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
-    <col min="4" max="12" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="48.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="39.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="36.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="24.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="24.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -4688,7 +4678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>124</v>
       </c>
@@ -4699,7 +4689,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>127</v>
       </c>
@@ -4710,7 +4700,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -4721,7 +4711,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -4732,7 +4722,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>135</v>
       </c>
@@ -4743,12 +4733,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="4" t="s">
         <v>305</v>
       </c>
@@ -4762,68 +4752,68 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C14" s="5">
-        <v>39.053254437869803</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="5" t="n">
+        <v>39.0532544378698</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="5">
-        <v>26.627218934911198</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="5" t="n">
+        <v>26.6272189349112</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C16" s="5">
-        <v>16.568047337278099</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="5" t="n">
+        <v>16.5680473372781</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="5" t="n">
         <v>17.7514792899408</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="5" t="n">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="3" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="4" t="s">
         <v>55</v>
       </c>
@@ -4837,138 +4827,138 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D23" s="5">
-        <v>82.248520710059196</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="5" t="n">
+        <v>82.2485207100592</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="5" t="n">
         <v>17.7514792899408</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D25" s="5">
-        <v>65.680473372781094</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="5" t="n">
+        <v>65.6804733727811</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D26" s="5">
-        <v>16.568047337278099</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="5" t="n">
+        <v>16.5680473372781</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D27" s="5">
-        <v>39.053254437869803</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="5" t="n">
+        <v>39.0532544378698</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D28" s="5">
-        <v>26.627218934911198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="5" t="n">
+        <v>26.6272189349112</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="D29" s="5">
-        <v>79.856115107913695</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="5" t="n">
+        <v>79.8561151079137</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D30" s="5">
-        <v>59.459459459459502</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D30" s="5" t="n">
+        <v>59.4594594594595</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="4" t="s">
         <v>195</v>
       </c>
@@ -5000,44 +4990,44 @@
         <v>324</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="s">
         <v>325</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="5">
-        <v>-197.77852387602201</v>
-      </c>
-      <c r="F35" s="5">
-        <v>413.55704775204299</v>
-      </c>
-      <c r="G35" s="5">
-        <v>441.72613618635103</v>
-      </c>
-      <c r="H35" s="5">
-        <v>11.346682588286599</v>
-      </c>
-      <c r="I35" s="5">
+      <c r="E35" s="5" t="n">
+        <v>-197.778523876022</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>413.557047752043</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>441.726136186351</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>11.3466825882866</v>
+      </c>
+      <c r="I35" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="5">
-        <v>9.9916110924389203E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="5" t="n">
+        <v>0.00999161109243892</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" s="4" t="s">
         <v>328</v>
       </c>
@@ -5069,7 +5059,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="s">
         <v>307</v>
       </c>
@@ -5079,29 +5069,29 @@
       <c r="C40" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D40" s="5">
-        <v>0.76093234290913503</v>
-      </c>
-      <c r="E40" s="5">
-        <v>0.20986644683436001</v>
-      </c>
-      <c r="F40" s="5">
+      <c r="D40" s="5" t="n">
+        <v>0.760932342909135</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.20986644683436</v>
+      </c>
+      <c r="F40" s="5" t="n">
         <v>3.62579323368309</v>
       </c>
-      <c r="G40" s="5">
-        <v>2.8807579294856E-4</v>
-      </c>
-      <c r="H40" s="5">
-        <v>2.1402707568201902</v>
-      </c>
-      <c r="I40" s="5">
+      <c r="G40" s="5" t="n">
+        <v>0.00028807579294856</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2.14027075682019</v>
+      </c>
+      <c r="I40" s="5" t="n">
         <v>1.41850239766936</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="5" t="n">
         <v>3.22929232973169</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="s">
         <v>307</v>
       </c>
@@ -5111,29 +5101,29 @@
       <c r="C41" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D41" s="5">
-        <v>-0.31150821771315101</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41" s="5" t="n">
+        <v>-0.311508217713151</v>
+      </c>
+      <c r="E41" s="5" t="n">
         <v>0.209833462173563</v>
       </c>
-      <c r="F41" s="5">
-        <v>-1.4845497685945299</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0.13766313016550799</v>
-      </c>
-      <c r="H41" s="5">
-        <v>0.73234159230750695</v>
-      </c>
-      <c r="I41" s="5">
-        <v>0.48540375670228603</v>
-      </c>
-      <c r="J41" s="5">
-        <v>1.1049032901334599</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="5" t="n">
+        <v>-1.48454976859453</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.137663130165508</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.732341592307507</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.485403756702286</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1.10490329013346</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="s">
         <v>308</v>
       </c>
@@ -5143,29 +5133,29 @@
       <c r="C42" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="5" t="n">
         <v>1.64579789150885</v>
       </c>
-      <c r="E42" s="5">
-        <v>0.40114440735704598</v>
-      </c>
-      <c r="F42" s="5">
-        <v>4.1027566664888697</v>
-      </c>
-      <c r="G42" s="5">
-        <v>4.0825655861020099E-5</v>
-      </c>
-      <c r="H42" s="5">
-        <v>5.1851454403946198</v>
-      </c>
-      <c r="I42" s="5">
-        <v>2.3621431007056199</v>
-      </c>
-      <c r="J42" s="5">
+      <c r="E42" s="5" t="n">
+        <v>0.401144407357046</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>4.10275666648887</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0000408256558610201</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>5.18514544039462</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>2.36214310070562</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>11.3819239952117</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="s">
         <v>308</v>
       </c>
@@ -5175,29 +5165,29 @@
       <c r="C43" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D43" s="5">
-        <v>0.96091747801553595</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.68501430986996703</v>
-      </c>
-      <c r="F43" s="5">
-        <v>1.4027699336645101</v>
-      </c>
-      <c r="G43" s="5">
-        <v>0.16068545545746499</v>
-      </c>
-      <c r="H43" s="5">
-        <v>2.6140937470755099</v>
-      </c>
-      <c r="I43" s="5">
-        <v>0.68270945978458497</v>
-      </c>
-      <c r="J43" s="5">
+      <c r="D43" s="5" t="n">
+        <v>0.960917478015536</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.685014309869967</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1.40276993366451</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.160685455457465</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2.61409374707551</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0.682709459784585</v>
+      </c>
+      <c r="J43" s="5" t="n">
         <v>10.0093619922235</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="s">
         <v>309</v>
       </c>
@@ -5207,29 +5197,29 @@
       <c r="C44" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D44" s="5">
-        <v>0.20061774111564601</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0.19382041324327301</v>
-      </c>
-      <c r="F44" s="5">
-        <v>1.0350702372295599</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0.30063611087605802</v>
-      </c>
-      <c r="H44" s="5">
-        <v>1.2221575019567901</v>
-      </c>
-      <c r="I44" s="5">
-        <v>0.83588579146513198</v>
-      </c>
-      <c r="J44" s="5">
+      <c r="D44" s="5" t="n">
+        <v>0.200617741115646</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.193820413243273</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1.03507023722956</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.300636110876058</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>1.22215750195679</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0.835885791465132</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>1.78692947629982</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="s">
         <v>309</v>
       </c>
@@ -5239,34 +5229,34 @@
       <c r="C45" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="5" t="n">
         <v>0.6758583758433</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>0.445300327280235</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="5" t="n">
         <v>1.51775854280469</v>
       </c>
-      <c r="G45" s="5">
-        <v>0.12907527972477401</v>
-      </c>
-      <c r="H45" s="5">
+      <c r="G45" s="5" t="n">
+        <v>0.129075279724774</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>1.96571957819761</v>
       </c>
-      <c r="I45" s="5">
-        <v>0.82126107155403105</v>
-      </c>
-      <c r="J45" s="5">
-        <v>4.7050244970185204</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I45" s="5" t="n">
+        <v>0.821261071554031</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>4.70502449701852</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" s="4" t="s">
         <v>334</v>
       </c>
@@ -5292,64 +5282,64 @@
         <v>211</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D50" s="5">
-        <v>-203.45186517016501</v>
-      </c>
-      <c r="E50" s="5">
-        <v>-197.77852387602201</v>
-      </c>
-      <c r="F50" s="5">
-        <v>11.346682588286599</v>
-      </c>
-      <c r="G50" s="5">
+      <c r="D50" s="5" t="n">
+        <v>-203.451865170165</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-197.778523876022</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>11.3466825882866</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="5">
-        <v>9.9916110924389203E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="5" t="n">
+        <v>0.00999161109243892</v>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D51" s="5">
-        <v>-216.38880844943401</v>
-      </c>
-      <c r="E51" s="5">
-        <v>-197.77852387602201</v>
-      </c>
-      <c r="F51" s="5">
-        <v>37.220569146825603</v>
-      </c>
-      <c r="G51" s="5">
+      <c r="D51" s="5" t="n">
+        <v>-216.388808449434</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-197.778523876022</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>37.2205691468256</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="5">
-        <v>4.1325511550434999E-8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H51" s="5" t="n">
+        <v>0.000000041325511550435</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" s="4" t="s">
         <v>332</v>
       </c>
@@ -5369,312 +5359,312 @@
         <v>345</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E56" s="5">
-        <v>0.74854009817498901</v>
+      <c r="E56" s="5" t="n">
+        <v>0.748540098174989</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E57" s="5">
-        <v>5.9667885002268099E-2</v>
+      <c r="E57" s="5" t="n">
+        <v>0.0596678850022681</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="5" t="n">
         <v>0.191792016822742</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E59" s="5">
-        <v>0.67151390727381199</v>
+      <c r="E59" s="5" t="n">
+        <v>0.671513907273812</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E60" s="5">
-        <v>0.11820624895401199</v>
+      <c r="E60" s="5" t="n">
+        <v>0.118206248954012</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E61" s="5">
-        <v>0.21027984377217601</v>
+      <c r="E61" s="5" t="n">
+        <v>0.210279843772176</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="5" t="n">
         <v>0.559414785467786</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="5" t="n">
         <v>0.226491581049719</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E64" s="5">
-        <v>0.21409363348249499</v>
+      <c r="E64" s="5" t="n">
+        <v>0.214093633482495</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E65" s="5">
-        <v>0.40321232959099501</v>
+      <c r="E65" s="5" t="n">
+        <v>0.403212329590995</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E66" s="5">
-        <v>0.40819240153959502</v>
+      <c r="E66" s="5" t="n">
+        <v>0.408192401539595</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="5" t="n">
         <v>55</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="5" t="n">
         <v>0.18859526886941</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="5" t="n">
         <v>61</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E68" s="5">
-        <v>0.22249827699085201</v>
+      <c r="E68" s="5" t="n">
+        <v>0.222498276990852</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="5" t="n">
         <v>61</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E69" s="5">
-        <v>0.65031235182331404</v>
+      <c r="E69" s="5" t="n">
+        <v>0.650312351823314</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="5" t="n">
         <v>61</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E70" s="5">
-        <v>0.12718937118583401</v>
+      <c r="E70" s="5" t="n">
+        <v>0.127189371185834</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" s="4" t="s">
         <v>328</v>
       </c>
@@ -5700,226 +5690,234 @@
         <v>369</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="30" customHeight="1">
       <c r="A75" s="5" t="s">
         <v>307</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C75" s="5">
-        <v>0.76093234290913503</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0.72615529144806101</v>
-      </c>
-      <c r="E75" s="5">
-        <v>2.1402707568201902</v>
-      </c>
-      <c r="F75" s="5">
-        <v>2.0671178445761802</v>
-      </c>
-      <c r="G75" s="5">
-        <v>3.47770514610743E-2</v>
-      </c>
-      <c r="H75" s="5">
-        <v>3.4179279425700702</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="5" t="n">
+        <v>0.760932342909135</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>0.726155291448061</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>2.14027075682019</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>2.06711784457618</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.0347770514610743</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>3.41792794257007</v>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="s">
         <v>307</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="5">
-        <v>-0.31150821771315101</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-0.28443370545572899</v>
-      </c>
-      <c r="E76" s="5">
-        <v>0.73234159230750695</v>
-      </c>
-      <c r="F76" s="5">
-        <v>0.75244023649312397</v>
-      </c>
-      <c r="G76" s="5">
-        <v>2.7074512257422498E-2</v>
-      </c>
-      <c r="H76" s="5">
-        <v>2.7444357109759698</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="5" t="n">
+        <v>-0.311508217713151</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>-0.284433705455729</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.732341592307507</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.752440236493124</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.0270745122574225</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>2.74443571097597</v>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
       <c r="A77" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="5" t="n">
         <v>1.64579789150885</v>
       </c>
-      <c r="D77" s="5">
-        <v>1.5536104009256999</v>
-      </c>
-      <c r="E77" s="5">
-        <v>5.1851454403946198</v>
-      </c>
-      <c r="F77" s="5">
-        <v>4.7285112228823598</v>
-      </c>
-      <c r="G77" s="5">
-        <v>9.21874905831499E-2</v>
-      </c>
-      <c r="H77" s="5">
-        <v>8.8065845550805708</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D77" s="5" t="n">
+        <v>1.5536104009257</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>5.18514544039462</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>4.72851122288236</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.0921874905831499</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>8.80658455508057</v>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
       <c r="A78" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C78" s="5">
-        <v>0.96091747801553595</v>
-      </c>
-      <c r="D78" s="5">
-        <v>0.73067917029697804</v>
-      </c>
-      <c r="E78" s="5">
-        <v>2.6140937470755099</v>
-      </c>
-      <c r="F78" s="5">
-        <v>2.0764904194836502</v>
-      </c>
-      <c r="G78" s="5">
-        <v>0.23023830771855799</v>
-      </c>
-      <c r="H78" s="5">
+      <c r="C78" s="5" t="n">
+        <v>0.960917478015536</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>0.730679170296978</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2.61409374707551</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>2.07649041948365</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.230238307718558</v>
+      </c>
+      <c r="H78" s="5" t="n">
         <v>20.5655718427581</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="30" customHeight="1">
       <c r="A79" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C79" s="5">
-        <v>0.20061774111564601</v>
-      </c>
-      <c r="D79" s="5">
+      <c r="C79" s="5" t="n">
+        <v>0.200617741115646</v>
+      </c>
+      <c r="D79" s="5" t="n">
         <v>0.193368834225632</v>
       </c>
-      <c r="E79" s="5">
-        <v>1.2221575019567901</v>
-      </c>
-      <c r="F79" s="5">
-        <v>1.2133302287146801</v>
-      </c>
-      <c r="G79" s="5">
-        <v>7.2489068900141503E-3</v>
-      </c>
-      <c r="H79" s="5">
-        <v>0.72226969338796698</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E79" s="5" t="n">
+        <v>1.22215750195679</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1.21333022871468</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.00724890689001415</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.722269693387967</v>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
       <c r="A80" s="5" t="s">
         <v>309</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C80" s="5">
+      <c r="C80" s="5" t="n">
         <v>0.6758583758433</v>
       </c>
-      <c r="D80" s="5">
-        <v>0.56022538931587995</v>
-      </c>
-      <c r="E80" s="5">
+      <c r="D80" s="5" t="n">
+        <v>0.56022538931588</v>
+      </c>
+      <c r="E80" s="5" t="n">
         <v>1.96571957819761</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="5" t="n">
         <v>1.751067127644</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="5" t="n">
         <v>0.11563298652742</v>
       </c>
-      <c r="H80" s="5">
+      <c r="H80" s="5" t="n">
         <v>10.919790031823</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:A87"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="9" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" s="3" t="s">
         <v>374</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="95.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="95.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>376</v>
       </c>
@@ -5936,7 +5934,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>381</v>
       </c>
@@ -5949,11 +5947,11 @@
       <c r="D4" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="5" t="n">
         <v>22.51</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>384</v>
       </c>
@@ -5966,11 +5964,11 @@
       <c r="D5" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>19.96</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>386</v>
       </c>
@@ -5983,11 +5981,11 @@
       <c r="D6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>13.35</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>388</v>
       </c>
@@ -6000,11 +5998,11 @@
       <c r="D7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>11.67</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>390</v>
       </c>
@@ -6017,11 +6015,11 @@
       <c r="D8" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>20.9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>392</v>
       </c>
@@ -6034,11 +6032,11 @@
       <c r="D9" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>235.21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>394</v>
       </c>
@@ -6051,11 +6049,11 @@
       <c r="D10" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>21.52</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>371</v>
       </c>
@@ -6068,11 +6066,11 @@
       <c r="D11" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>149.06</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>372</v>
       </c>
@@ -6085,11 +6083,11 @@
       <c r="D12" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>131.75</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>373</v>
       </c>
@@ -6102,11 +6100,11 @@
       <c r="D13" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>207.66</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>374</v>
       </c>
@@ -6119,12 +6117,12 @@
       <c r="D14" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="5" t="n">
         <v>368.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>